--- a/Design/config/WorldConfig.xlsx
+++ b/Design/config/WorldConfig.xlsx
@@ -1342,7 +1342,7 @@
         <v>70</v>
       </c>
       <c r="P5" s="4">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="Q5" s="6" t="s">
         <v>145</v>
@@ -1398,7 +1398,7 @@
         <v>80</v>
       </c>
       <c r="P6" s="4">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="Q6" s="6" t="s">
         <v>143</v>
@@ -1454,7 +1454,7 @@
         <v>75</v>
       </c>
       <c r="P7" s="4">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>144</v>
@@ -1512,7 +1512,7 @@
         <v>90</v>
       </c>
       <c r="P8" s="4">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="Q8" s="6" t="s">
         <v>170</v>
@@ -1570,7 +1570,7 @@
         <v>80</v>
       </c>
       <c r="P9" s="4">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>148</v>
@@ -1628,7 +1628,7 @@
         <v>70</v>
       </c>
       <c r="P10" s="4">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>149</v>
@@ -1686,7 +1686,7 @@
         <v>70</v>
       </c>
       <c r="P11" s="4">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>150</v>
@@ -1744,7 +1744,7 @@
         <v>75</v>
       </c>
       <c r="P12" s="4">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>151</v>
@@ -1802,7 +1802,7 @@
         <v>65</v>
       </c>
       <c r="P13" s="4">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>153</v>
@@ -1860,7 +1860,7 @@
         <v>75</v>
       </c>
       <c r="P14" s="4">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>154</v>
@@ -1918,7 +1918,7 @@
         <v>70</v>
       </c>
       <c r="P15" s="4">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>155</v>
@@ -1976,7 +1976,7 @@
         <v>85</v>
       </c>
       <c r="P16" s="4">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>132</v>
@@ -2034,7 +2034,7 @@
         <v>90</v>
       </c>
       <c r="P17" s="4">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>156</v>
@@ -2092,7 +2092,7 @@
         <v>85</v>
       </c>
       <c r="P18" s="4">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>157</v>
@@ -2150,7 +2150,7 @@
         <v>80</v>
       </c>
       <c r="P19" s="4">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>158</v>
@@ -2208,7 +2208,7 @@
         <v>70</v>
       </c>
       <c r="P20" s="4">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>171</v>
@@ -2266,7 +2266,7 @@
         <v>80</v>
       </c>
       <c r="P21" s="4">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>134</v>
@@ -2324,7 +2324,7 @@
         <v>75</v>
       </c>
       <c r="P22" s="4">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>159</v>
@@ -2382,7 +2382,7 @@
         <v>85</v>
       </c>
       <c r="P23" s="4">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>165</v>
@@ -2440,7 +2440,7 @@
         <v>95</v>
       </c>
       <c r="P24" s="4">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>169</v>
@@ -2498,7 +2498,7 @@
         <v>90</v>
       </c>
       <c r="P25" s="4">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>161</v>
@@ -2556,7 +2556,7 @@
         <v>75</v>
       </c>
       <c r="P26" s="4">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>162</v>
@@ -2614,7 +2614,7 @@
         <v>75</v>
       </c>
       <c r="P27" s="4">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="Q27" s="6" t="s">
         <v>163</v>
@@ -2672,7 +2672,7 @@
         <v>70</v>
       </c>
       <c r="P28" s="4">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="Q28" s="6" t="s">
         <v>164</v>
@@ -2730,7 +2730,7 @@
         <v>70</v>
       </c>
       <c r="P29" s="4">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="Q29" s="6" t="s">
         <v>135</v>
@@ -2788,7 +2788,7 @@
         <v>65</v>
       </c>
       <c r="P30" s="4">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="Q30" s="6" t="s">
         <v>137</v>
@@ -2846,7 +2846,7 @@
         <v>75</v>
       </c>
       <c r="P31" s="4">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>138</v>
@@ -2904,7 +2904,7 @@
         <v>85</v>
       </c>
       <c r="P32" s="4">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Q32" s="6" t="s">
         <v>146</v>
@@ -2962,7 +2962,7 @@
         <v>80</v>
       </c>
       <c r="P33" s="4">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>167</v>
@@ -3020,7 +3020,7 @@
         <v>75</v>
       </c>
       <c r="P34" s="4">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>136</v>
@@ -3078,7 +3078,7 @@
         <v>70</v>
       </c>
       <c r="P35" s="4">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>139</v>
@@ -3136,7 +3136,7 @@
         <v>60</v>
       </c>
       <c r="P36" s="4">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>140</v>
@@ -3194,7 +3194,7 @@
         <v>85</v>
       </c>
       <c r="P37" s="4">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>166</v>
@@ -3252,7 +3252,7 @@
         <v>55</v>
       </c>
       <c r="P38" s="4">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>131</v>
@@ -3310,7 +3310,7 @@
         <v>75</v>
       </c>
       <c r="P39" s="4">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="Q39" s="6" t="s">
         <v>141</v>
@@ -3368,7 +3368,7 @@
         <v>65</v>
       </c>
       <c r="P40" s="4">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="Q40" s="6" t="s">
         <v>147</v>
@@ -3426,7 +3426,7 @@
         <v>80</v>
       </c>
       <c r="P41" s="4">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="Q41" s="6" t="s">
         <v>142</v>
@@ -3484,7 +3484,7 @@
         <v>75</v>
       </c>
       <c r="P42" s="4">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>168</v>
@@ -3542,7 +3542,7 @@
         <v>80</v>
       </c>
       <c r="P43" s="4">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="Q43" s="6" t="s">
         <v>152</v>
@@ -3600,7 +3600,7 @@
         <v>80</v>
       </c>
       <c r="P44" s="4">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>133</v>
@@ -3658,7 +3658,7 @@
         <v>80</v>
       </c>
       <c r="P45" s="4">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>160</v>
@@ -3716,7 +3716,7 @@
         <v>70</v>
       </c>
       <c r="P46" s="4">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="Q46" s="6">
         <v>10034</v>

--- a/Design/config/WorldConfig.xlsx
+++ b/Design/config/WorldConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="182">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -466,168 +466,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>10006</t>
-  </si>
-  <si>
-    <t>10021,10025,10028</t>
-  </si>
-  <si>
-    <t>10036,10037,10032</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10031,10035,10034,10036</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10003,10002,10004,10005,10030</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,10004,10005,10009,10015,10016</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,10023</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,10001,10015,10026,10029,10030</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,10006,10007,10001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10005,10007,10008</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,10007,10010,10016</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10009,10016,10039,10041</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10012,10022,10017,10038,10020</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10011,10019,10020,10031,10035</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10015,10018,10014,10017,10026</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,10004,10013,10016,10018,10026</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,10009,10010,10015,10018,10039</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10016,10013,10015,10017,10038,10039</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10012,10021,10031</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10011,10012,10021,10022</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10022,10019,10020,10027,10028</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10014,10011,10020,10021,10024,10026,10028</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10003,10030</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10022,10026,10028,10029</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10027,10028,10029</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10022,10024,10025,10027,10029,10021</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,10024,10026,10028,10030,10025</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,10004,10023,10029</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10035,10038,10039,10036</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10032,10035,10033,10034</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10010,10033,10038,10040,10016,10018</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10042,10039,10041</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10010,10040</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10041,10040</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10012,10032,10033,10031,10036,10038</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10005,10006,10009</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,10015,10022,10024,10029,10013,10014</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10013,10026,10017,10022,10024</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10018,10033,10035,10039,10011,10017</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10011,10014,10013,10018,10038</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10012,10019,10035,10032</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>changsha</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -662,6 +500,132 @@
   <si>
     <t>新野</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10040</t>
+  </si>
+  <si>
+    <t>10026,10015</t>
+  </si>
+  <si>
+    <t>10017,10019,10018,10040</t>
+  </si>
+  <si>
+    <t>10032</t>
+  </si>
+  <si>
+    <t>10019,10020,10021,10041</t>
+  </si>
+  <si>
+    <t>10012,10013,10014</t>
+  </si>
+  <si>
+    <t>10039,10029,10013,10014</t>
+  </si>
+  <si>
+    <t>10016,10019,10040,10041</t>
+  </si>
+  <si>
+    <t>10024,10021,10023</t>
+  </si>
+  <si>
+    <t>10003,10008,10016</t>
+  </si>
+  <si>
+    <t>10041,10042,10017</t>
+  </si>
+  <si>
+    <t>10027,10010,10029,10013,10015,10011</t>
+  </si>
+  <si>
+    <t>10037,10018,10020,10022,10036,10005</t>
+  </si>
+  <si>
+    <t>10025,10027,10009,10014</t>
+  </si>
+  <si>
+    <t>10031,10032,10035</t>
+  </si>
+  <si>
+    <t>10003,10039,10004,10020,10007</t>
+  </si>
+  <si>
+    <t>10035,10036,10021,10023</t>
+  </si>
+  <si>
+    <t>10030,10025,10028,10029,10014,10015</t>
+  </si>
+  <si>
+    <t>10027,10028,10039,10010,10014,10001,10038</t>
+  </si>
+  <si>
+    <t>10030,10032,10033,10025</t>
+  </si>
+  <si>
+    <t>10031,10033,10034</t>
+  </si>
+  <si>
+    <t>10039,10010,10011,10012,10014,10008</t>
+  </si>
+  <si>
+    <t>10025,10009</t>
+  </si>
+  <si>
+    <t>10005,10018,10019,10021,10002,10004</t>
+  </si>
+  <si>
+    <t>10003,10006,10019,10017</t>
+  </si>
+  <si>
+    <t>10002,10006,10007,10016,10019</t>
+  </si>
+  <si>
+    <t>10001,10029,10004,10039,10010</t>
+  </si>
+  <si>
+    <t>10030,10035,10037,10028,10005,10021</t>
+  </si>
+  <si>
+    <t>10038,10002,10007,10008,10010,10029,10013</t>
+  </si>
+  <si>
+    <t>10037,10022</t>
+  </si>
+  <si>
+    <t>10036,10001,10028,10004,10020,10021</t>
+  </si>
+  <si>
+    <t>10008,10011,10013</t>
+  </si>
+  <si>
+    <t>10026,10030,10027,10031,10015</t>
+  </si>
+  <si>
+    <t>10023,10022</t>
+  </si>
+  <si>
+    <t>10030,10027,10001,10036,10005,10029</t>
+  </si>
+  <si>
+    <t>10002,10003,10008,10039</t>
+  </si>
+  <si>
+    <t>10039,10006,10007,10012,10013</t>
+  </si>
+  <si>
+    <t>10028,10005,10038,10004,10029</t>
+  </si>
+  <si>
+    <t>10002,10038,10001,10005,10020</t>
+  </si>
+  <si>
+    <t>10003,10017,10018,10016,10041,10020</t>
+  </si>
+  <si>
+    <t>10025,10027,10031,10035,10028,10036</t>
+  </si>
+  <si>
+    <t>10030,10033,10037,10036</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1067,11 +1031,12 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="9.625" customWidth="1"/>
-    <col min="17" max="17" width="24.375" customWidth="1"/>
+    <col min="8" max="16" width="9" customWidth="1"/>
+    <col min="17" max="17" width="49.375" customWidth="1"/>
     <col min="18" max="18" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1092,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1183,7 +1148,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1239,7 +1204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1295,7 +1260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10001</v>
       </c>
@@ -1303,7 +1268,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="D5" s="4">
         <v>789</v>
@@ -1345,13 +1310,13 @@
         <v>180</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10002</v>
       </c>
@@ -1401,13 +1366,13 @@
         <v>210</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10003</v>
       </c>
@@ -1457,15 +1422,15 @@
         <v>195</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM7" s="5"/>
-      <c r="AN7" s="5"/>
-    </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10004</v>
       </c>
@@ -1515,15 +1480,15 @@
         <v>240</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM8" s="5"/>
-      <c r="AN8" s="5"/>
-    </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="AJ8" s="5"/>
+      <c r="AK8" s="5"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10005</v>
       </c>
@@ -1573,15 +1538,15 @@
         <v>225</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM9" s="5"/>
-      <c r="AN9" s="5"/>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="5"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10006</v>
       </c>
@@ -1636,10 +1601,10 @@
       <c r="R10" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM10" s="5"/>
-      <c r="AN10" s="5"/>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ10" s="5"/>
+      <c r="AK10" s="5"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10007</v>
       </c>
@@ -1689,15 +1654,15 @@
         <v>180</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM11" s="5"/>
-      <c r="AN11" s="5"/>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ11" s="5"/>
+      <c r="AK11" s="5"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>10008</v>
       </c>
@@ -1747,15 +1712,15 @@
         <v>210</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM12" s="5"/>
-      <c r="AN12" s="5"/>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ12" s="5"/>
+      <c r="AK12" s="5"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>10009</v>
       </c>
@@ -1805,15 +1770,15 @@
         <v>165</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM13" s="5"/>
-      <c r="AN13" s="5"/>
-    </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="AJ13" s="5"/>
+      <c r="AK13" s="5"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10010</v>
       </c>
@@ -1863,15 +1828,15 @@
         <v>210</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="R14" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM14" s="5"/>
-      <c r="AN14" s="5"/>
-    </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ14" s="5"/>
+      <c r="AK14" s="5"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>10011</v>
       </c>
@@ -1921,15 +1886,15 @@
         <v>180</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="R15" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AM15" s="5"/>
-      <c r="AN15" s="5"/>
-    </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ15" s="5"/>
+      <c r="AK15" s="5"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10012</v>
       </c>
@@ -1979,15 +1944,15 @@
         <v>240</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM16" s="5"/>
-      <c r="AN16" s="5"/>
-    </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="AJ16" s="5"/>
+      <c r="AK16" s="5"/>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>10013</v>
       </c>
@@ -2037,15 +2002,15 @@
         <v>255</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="R17" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AM17" s="5"/>
-      <c r="AN17" s="5"/>
-    </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ17" s="5"/>
+      <c r="AK17" s="5"/>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>10014</v>
       </c>
@@ -2095,15 +2060,15 @@
         <v>270</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="R18" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AM18" s="5"/>
-      <c r="AN18" s="5"/>
-    </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="5"/>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>10015</v>
       </c>
@@ -2153,15 +2118,15 @@
         <v>225</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AM19" s="5"/>
-      <c r="AN19" s="5"/>
-    </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+      <c r="AJ19" s="5"/>
+      <c r="AK19" s="5"/>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>10016</v>
       </c>
@@ -2211,15 +2176,15 @@
         <v>195</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="AM20" s="5"/>
-      <c r="AN20" s="5"/>
-    </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="AJ20" s="5"/>
+      <c r="AK20" s="5"/>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>10017</v>
       </c>
@@ -2269,15 +2234,15 @@
         <v>225</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="R21" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM21" s="5"/>
-      <c r="AN21" s="5"/>
-    </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ21" s="5"/>
+      <c r="AK21" s="5"/>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>10018</v>
       </c>
@@ -2327,15 +2292,15 @@
         <v>240</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="AM22" s="5"/>
-      <c r="AN22" s="5"/>
-    </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="AJ22" s="5"/>
+      <c r="AK22" s="5"/>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>10019</v>
       </c>
@@ -2385,15 +2350,15 @@
         <v>270</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="R23" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AM23" s="5"/>
-      <c r="AN23" s="5"/>
-    </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ23" s="5"/>
+      <c r="AK23" s="5"/>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>10020</v>
       </c>
@@ -2443,15 +2408,15 @@
         <v>285</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM24" s="5"/>
-      <c r="AN24" s="5"/>
-    </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="AJ24" s="5"/>
+      <c r="AK24" s="5"/>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>10021</v>
       </c>
@@ -2501,15 +2466,15 @@
         <v>270</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM25" s="5"/>
-      <c r="AN25" s="5"/>
-    </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="AJ25" s="5"/>
+      <c r="AK25" s="5"/>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>10022</v>
       </c>
@@ -2559,15 +2524,15 @@
         <v>240</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AM26" s="5"/>
-      <c r="AN26" s="5"/>
-    </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="AJ26" s="5"/>
+      <c r="AK26" s="5"/>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>10023</v>
       </c>
@@ -2617,15 +2582,15 @@
         <v>255</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AM27" s="5"/>
-      <c r="AN27" s="5"/>
-    </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="AJ27" s="5"/>
+      <c r="AK27" s="5"/>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>10024</v>
       </c>
@@ -2675,15 +2640,15 @@
         <v>240</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AM28" s="5"/>
-      <c r="AN28" s="5"/>
-    </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="AJ28" s="5"/>
+      <c r="AK28" s="5"/>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>10025</v>
       </c>
@@ -2733,15 +2698,15 @@
         <v>180</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM29" s="5"/>
-      <c r="AN29" s="5"/>
-    </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+      <c r="AJ29" s="5"/>
+      <c r="AK29" s="5"/>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>10026</v>
       </c>
@@ -2791,15 +2756,15 @@
         <v>165</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM30" s="5"/>
-      <c r="AN30" s="5"/>
-    </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+      <c r="AJ30" s="5"/>
+      <c r="AK30" s="5"/>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>10027</v>
       </c>
@@ -2849,15 +2814,15 @@
         <v>210</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="R31" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM31" s="5"/>
-      <c r="AN31" s="5"/>
-    </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ31" s="5"/>
+      <c r="AK31" s="5"/>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>10028</v>
       </c>
@@ -2907,15 +2872,15 @@
         <v>270</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="AM32" s="5"/>
-      <c r="AN32" s="5"/>
-    </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+      <c r="AJ32" s="5"/>
+      <c r="AK32" s="5"/>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>10029</v>
       </c>
@@ -2965,15 +2930,15 @@
         <v>255</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM33" s="5"/>
-      <c r="AN33" s="5"/>
-    </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="AJ33" s="5"/>
+      <c r="AK33" s="5"/>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>10030</v>
       </c>
@@ -3023,15 +2988,15 @@
         <v>240</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM34" s="5"/>
-      <c r="AN34" s="5"/>
-    </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+      <c r="AJ34" s="5"/>
+      <c r="AK34" s="5"/>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>10031</v>
       </c>
@@ -3081,15 +3046,15 @@
         <v>195</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM35" s="5"/>
-      <c r="AN35" s="5"/>
-    </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="AJ35" s="5"/>
+      <c r="AK35" s="5"/>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>10032</v>
       </c>
@@ -3139,15 +3104,15 @@
         <v>150</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="R36" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM36" s="5"/>
-      <c r="AN36" s="5"/>
-    </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="AJ36" s="5"/>
+      <c r="AK36" s="5"/>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>10033</v>
       </c>
@@ -3197,15 +3162,15 @@
         <v>225</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="R37" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM37" s="5"/>
-      <c r="AN37" s="5"/>
-    </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ37" s="5"/>
+      <c r="AK37" s="5"/>
+    </row>
+    <row r="38" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>10034</v>
       </c>
@@ -3255,15 +3220,15 @@
         <v>135</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="R38" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM38" s="5"/>
-      <c r="AN38" s="5"/>
-    </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="AJ38" s="5"/>
+      <c r="AK38" s="5"/>
+    </row>
+    <row r="39" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>10035</v>
       </c>
@@ -3313,15 +3278,15 @@
         <v>225</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM39" s="5"/>
-      <c r="AN39" s="5"/>
-    </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="AJ39" s="5"/>
+      <c r="AK39" s="5"/>
+    </row>
+    <row r="40" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>10036</v>
       </c>
@@ -3371,15 +3336,15 @@
         <v>180</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM40" s="5"/>
-      <c r="AN40" s="5"/>
-    </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="AJ40" s="5"/>
+      <c r="AK40" s="5"/>
+    </row>
+    <row r="41" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>10037</v>
       </c>
@@ -3429,15 +3394,15 @@
         <v>255</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="R41" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM41" s="5"/>
-      <c r="AN41" s="5"/>
-    </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ41" s="5"/>
+      <c r="AK41" s="5"/>
+    </row>
+    <row r="42" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>10038</v>
       </c>
@@ -3487,15 +3452,15 @@
         <v>195</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R42" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="AM42" s="5"/>
-      <c r="AN42" s="5"/>
-    </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="AJ42" s="5"/>
+      <c r="AK42" s="5"/>
+    </row>
+    <row r="43" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>10039</v>
       </c>
@@ -3545,15 +3510,15 @@
         <v>225</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="R43" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM43" s="5"/>
-      <c r="AN43" s="5"/>
-    </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ43" s="5"/>
+      <c r="AK43" s="5"/>
+    </row>
+    <row r="44" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>10040</v>
       </c>
@@ -3603,15 +3568,15 @@
         <v>255</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="R44" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AM44" s="5"/>
-      <c r="AN44" s="5"/>
-    </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ44" s="5"/>
+      <c r="AK44" s="5"/>
+    </row>
+    <row r="45" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>10041</v>
       </c>
@@ -3661,15 +3626,15 @@
         <v>255</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="R45" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AM45" s="5"/>
-      <c r="AN45" s="5"/>
-    </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AJ45" s="5"/>
+      <c r="AK45" s="5"/>
+    </row>
+    <row r="46" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>10042</v>
       </c>
@@ -3677,7 +3642,7 @@
         <v>94</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="D46" s="4">
         <v>1558</v>
@@ -3718,32 +3683,29 @@
       <c r="P46" s="4">
         <v>225</v>
       </c>
-      <c r="Q46" s="6">
-        <v>10034</v>
+      <c r="Q46" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="R46" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AM46" s="5"/>
-      <c r="AN46" s="5"/>
-    </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="AM47" s="5"/>
-      <c r="AN47" s="5"/>
-    </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="AM48" s="5"/>
-      <c r="AN48" s="5"/>
+      <c r="AJ46" s="5"/>
+      <c r="AK46" s="5"/>
+    </row>
+    <row r="47" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AJ47" s="5"/>
+      <c r="AK47" s="5"/>
+    </row>
+    <row r="48" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AJ48" s="5"/>
+      <c r="AK48" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:R4">
-    <sortState ref="A5:T46">
-      <sortCondition ref="H4"/>
+    <sortState ref="A5:R46">
+      <sortCondition ref="A4"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A5:Q43">
-    <sortCondition ref="A41"/>
-  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Design/config/WorldConfig.xlsx
+++ b/Design/config/WorldConfig.xlsx
@@ -589,9 +589,6 @@
     <t>10038,10002,10007,10008,10010,10029,10013</t>
   </si>
   <si>
-    <t>10037,10022</t>
-  </si>
-  <si>
     <t>10036,10001,10028,10004,10020,10021</t>
   </si>
   <si>
@@ -626,6 +623,10 @@
   </si>
   <si>
     <t>10030,10033,10037,10036</t>
+  </si>
+  <si>
+    <t>10037,10022,10024</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1301,7 +1302,7 @@
         <v>1700</v>
       </c>
       <c r="N5" s="4">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="O5" s="4">
         <v>70</v>
@@ -1310,7 +1311,7 @@
         <v>180</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>132</v>
@@ -1480,7 +1481,7 @@
         <v>240</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>134</v>
@@ -1538,7 +1539,7 @@
         <v>225</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>125</v>
@@ -1654,7 +1655,7 @@
         <v>180</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>125</v>
@@ -1712,7 +1713,7 @@
         <v>210</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>125</v>
@@ -1944,7 +1945,7 @@
         <v>240</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R16" s="4" t="s">
         <v>133</v>
@@ -2350,7 +2351,7 @@
         <v>270</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R23" s="4" t="s">
         <v>127</v>
@@ -2582,7 +2583,7 @@
         <v>255</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="R27" s="4" t="s">
         <v>135</v>
@@ -2640,7 +2641,7 @@
         <v>240</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R28" s="4" t="s">
         <v>135</v>
@@ -2698,7 +2699,7 @@
         <v>180</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R29" s="4" t="s">
         <v>131</v>
@@ -2863,7 +2864,7 @@
         <v>2800</v>
       </c>
       <c r="N32" s="4">
-        <v>4750</v>
+        <v>6000</v>
       </c>
       <c r="O32" s="4">
         <v>85</v>
@@ -2872,7 +2873,7 @@
         <v>270</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R32" s="4" t="s">
         <v>137</v>
@@ -2988,7 +2989,7 @@
         <v>240</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R34" s="4" t="s">
         <v>131</v>
@@ -3278,7 +3279,7 @@
         <v>225</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R39" s="4" t="s">
         <v>133</v>

--- a/Design/config/WorldConfig.xlsx
+++ b/Design/config/WorldConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$R$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$S$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="219">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -626,6 +626,154 @@
   </si>
   <si>
     <t>10037,10022,10024</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mini地图偏移</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MiniMapOffsets</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26,-20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-24,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,-10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-10,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-20,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,-15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-15,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-15,-10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-10,-10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-20,40</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-15,5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-40,-23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25,15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,-15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>12,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,-5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,-15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5,-5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,-8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-10,15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7,-10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,-7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17,7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-30,0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1024,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AL48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1034,10 +1182,11 @@
     <col min="7" max="7" width="9.625" customWidth="1"/>
     <col min="8" max="16" width="9" customWidth="1"/>
     <col min="17" max="17" width="49.375" customWidth="1"/>
-    <col min="18" max="18" width="12.125" customWidth="1"/>
+    <col min="18" max="18" width="12.75" customWidth="1"/>
+    <col min="19" max="19" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1090,10 +1239,13 @@
         <v>128</v>
       </c>
       <c r="R1" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1146,10 +1298,13 @@
         <v>129</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1202,10 +1357,13 @@
         <v>130</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1258,10 +1416,13 @@
         <v>8</v>
       </c>
       <c r="R4" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10001</v>
       </c>
@@ -1313,11 +1474,12 @@
       <c r="Q5" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="6"/>
+      <c r="S5" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10002</v>
       </c>
@@ -1369,11 +1531,14 @@
       <c r="Q6" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="R6" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10003</v>
       </c>
@@ -1425,13 +1590,16 @@
       <c r="Q7" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="R7" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="S7" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ7" s="5"/>
       <c r="AK7" s="5"/>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL7" s="5"/>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10004</v>
       </c>
@@ -1483,13 +1651,16 @@
       <c r="Q8" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="R8" s="4" t="s">
+      <c r="R8" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="S8" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AJ8" s="5"/>
       <c r="AK8" s="5"/>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL8" s="5"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10005</v>
       </c>
@@ -1541,13 +1712,16 @@
       <c r="Q9" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="R9" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="S9" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ9" s="5"/>
       <c r="AK9" s="5"/>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL9" s="5"/>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10006</v>
       </c>
@@ -1599,13 +1773,14 @@
       <c r="Q10" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="R10" s="6"/>
+      <c r="S10" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ10" s="5"/>
       <c r="AK10" s="5"/>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL10" s="5"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10007</v>
       </c>
@@ -1657,13 +1832,16 @@
       <c r="Q11" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="R11" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="S11" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ11" s="5"/>
       <c r="AK11" s="5"/>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL11" s="5"/>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>10008</v>
       </c>
@@ -1715,13 +1893,16 @@
       <c r="Q12" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="R12" s="4" t="s">
+      <c r="R12" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="S12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ12" s="5"/>
       <c r="AK12" s="5"/>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL12" s="5"/>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>10009</v>
       </c>
@@ -1773,13 +1954,14 @@
       <c r="Q13" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="R13" s="4" t="s">
+      <c r="R13" s="6"/>
+      <c r="S13" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AJ13" s="5"/>
       <c r="AK13" s="5"/>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL13" s="5"/>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10010</v>
       </c>
@@ -1831,13 +2013,16 @@
       <c r="Q14" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="S14" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ14" s="5"/>
       <c r="AK14" s="5"/>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL14" s="5"/>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>10011</v>
       </c>
@@ -1889,13 +2074,14 @@
       <c r="Q15" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="R15" s="6"/>
+      <c r="S15" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AJ15" s="5"/>
       <c r="AK15" s="5"/>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL15" s="5"/>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10012</v>
       </c>
@@ -1947,13 +2133,16 @@
       <c r="Q16" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="R16" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="S16" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AJ16" s="5"/>
       <c r="AK16" s="5"/>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL16" s="5"/>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>10013</v>
       </c>
@@ -2005,13 +2194,16 @@
       <c r="Q17" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="R17" s="4" t="s">
+      <c r="R17" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="S17" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AJ17" s="5"/>
       <c r="AK17" s="5"/>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL17" s="5"/>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>10014</v>
       </c>
@@ -2063,13 +2255,16 @@
       <c r="Q18" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="R18" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="S18" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AJ18" s="5"/>
       <c r="AK18" s="5"/>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL18" s="5"/>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>10015</v>
       </c>
@@ -2121,13 +2316,16 @@
       <c r="Q19" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="R19" s="4" t="s">
+      <c r="R19" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="S19" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="AJ19" s="5"/>
       <c r="AK19" s="5"/>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL19" s="5"/>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>10016</v>
       </c>
@@ -2179,13 +2377,14 @@
       <c r="Q20" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="R20" s="4" t="s">
+      <c r="R20" s="6"/>
+      <c r="S20" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ20" s="5"/>
       <c r="AK20" s="5"/>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL20" s="5"/>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>10017</v>
       </c>
@@ -2237,13 +2436,16 @@
       <c r="Q21" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="R21" s="4" t="s">
+      <c r="R21" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="S21" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ21" s="5"/>
       <c r="AK21" s="5"/>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL21" s="5"/>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>10018</v>
       </c>
@@ -2295,13 +2497,16 @@
       <c r="Q22" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="R22" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="S22" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ22" s="5"/>
       <c r="AK22" s="5"/>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL22" s="5"/>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>10019</v>
       </c>
@@ -2353,13 +2558,16 @@
       <c r="Q23" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="R23" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="S23" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AJ23" s="5"/>
       <c r="AK23" s="5"/>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL23" s="5"/>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>10020</v>
       </c>
@@ -2411,13 +2619,16 @@
       <c r="Q24" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="R24" s="4" t="s">
+      <c r="R24" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="S24" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AJ24" s="5"/>
       <c r="AK24" s="5"/>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL24" s="5"/>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>10021</v>
       </c>
@@ -2469,13 +2680,16 @@
       <c r="Q25" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="R25" s="4" t="s">
+      <c r="R25" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="S25" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AJ25" s="5"/>
       <c r="AK25" s="5"/>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL25" s="5"/>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>10022</v>
       </c>
@@ -2527,13 +2741,16 @@
       <c r="Q26" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="R26" s="4" t="s">
+      <c r="R26" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="S26" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="AJ26" s="5"/>
       <c r="AK26" s="5"/>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL26" s="5"/>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>10023</v>
       </c>
@@ -2585,13 +2802,16 @@
       <c r="Q27" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="R27" s="4" t="s">
+      <c r="R27" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="S27" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="AJ27" s="5"/>
       <c r="AK27" s="5"/>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL27" s="5"/>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>10024</v>
       </c>
@@ -2643,13 +2863,16 @@
       <c r="Q28" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="R28" s="4" t="s">
+      <c r="R28" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="S28" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="AJ28" s="5"/>
       <c r="AK28" s="5"/>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL28" s="5"/>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>10025</v>
       </c>
@@ -2701,13 +2924,16 @@
       <c r="Q29" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="R29" s="4" t="s">
+      <c r="R29" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="S29" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="AJ29" s="5"/>
       <c r="AK29" s="5"/>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL29" s="5"/>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>10026</v>
       </c>
@@ -2759,13 +2985,16 @@
       <c r="Q30" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="R30" s="4" t="s">
+      <c r="R30" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="S30" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="AJ30" s="5"/>
       <c r="AK30" s="5"/>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL30" s="5"/>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>10027</v>
       </c>
@@ -2817,13 +3046,16 @@
       <c r="Q31" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="R31" s="4" t="s">
+      <c r="R31" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="S31" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ31" s="5"/>
       <c r="AK31" s="5"/>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL31" s="5"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>10028</v>
       </c>
@@ -2875,13 +3107,16 @@
       <c r="Q32" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="R32" s="4" t="s">
+      <c r="R32" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="S32" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="AJ32" s="5"/>
       <c r="AK32" s="5"/>
-    </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL32" s="5"/>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>10029</v>
       </c>
@@ -2933,13 +3168,16 @@
       <c r="Q33" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="R33" s="4" t="s">
+      <c r="R33" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="S33" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AJ33" s="5"/>
       <c r="AK33" s="5"/>
-    </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL33" s="5"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>10030</v>
       </c>
@@ -2991,13 +3229,16 @@
       <c r="Q34" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="R34" s="4" t="s">
+      <c r="R34" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="S34" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="AJ34" s="5"/>
       <c r="AK34" s="5"/>
-    </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL34" s="5"/>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>10031</v>
       </c>
@@ -3049,13 +3290,16 @@
       <c r="Q35" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="R35" s="4" t="s">
+      <c r="R35" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="S35" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AJ35" s="5"/>
       <c r="AK35" s="5"/>
-    </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL35" s="5"/>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>10032</v>
       </c>
@@ -3107,13 +3351,16 @@
       <c r="Q36" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="R36" s="4" t="s">
+      <c r="R36" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="S36" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AJ36" s="5"/>
       <c r="AK36" s="5"/>
-    </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL36" s="5"/>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>10033</v>
       </c>
@@ -3165,13 +3412,16 @@
       <c r="Q37" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="R37" s="4" t="s">
+      <c r="R37" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="S37" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ37" s="5"/>
       <c r="AK37" s="5"/>
-    </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL37" s="5"/>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>10034</v>
       </c>
@@ -3223,13 +3473,16 @@
       <c r="Q38" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="R38" s="4" t="s">
+      <c r="R38" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="S38" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AJ38" s="5"/>
       <c r="AK38" s="5"/>
-    </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL38" s="5"/>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>10035</v>
       </c>
@@ -3281,13 +3534,14 @@
       <c r="Q39" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="R39" s="4" t="s">
+      <c r="R39" s="6"/>
+      <c r="S39" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AJ39" s="5"/>
       <c r="AK39" s="5"/>
-    </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL39" s="5"/>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>10036</v>
       </c>
@@ -3339,13 +3593,16 @@
       <c r="Q40" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="R40" s="4" t="s">
+      <c r="R40" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="S40" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AJ40" s="5"/>
       <c r="AK40" s="5"/>
-    </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL40" s="5"/>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>10037</v>
       </c>
@@ -3397,13 +3654,16 @@
       <c r="Q41" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="R41" s="4" t="s">
+      <c r="R41" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="S41" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ41" s="5"/>
       <c r="AK41" s="5"/>
-    </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL41" s="5"/>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>10038</v>
       </c>
@@ -3455,13 +3715,16 @@
       <c r="Q42" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="R42" s="4" t="s">
+      <c r="R42" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="S42" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ42" s="5"/>
       <c r="AK42" s="5"/>
-    </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL42" s="5"/>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>10039</v>
       </c>
@@ -3513,13 +3776,16 @@
       <c r="Q43" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="R43" s="4" t="s">
+      <c r="R43" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="S43" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ43" s="5"/>
       <c r="AK43" s="5"/>
-    </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL43" s="5"/>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>10040</v>
       </c>
@@ -3571,13 +3837,14 @@
       <c r="Q44" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="R44" s="4" t="s">
+      <c r="R44" s="6"/>
+      <c r="S44" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AJ44" s="5"/>
       <c r="AK44" s="5"/>
-    </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL44" s="5"/>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>10041</v>
       </c>
@@ -3629,13 +3896,16 @@
       <c r="Q45" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="R45" s="4" t="s">
+      <c r="R45" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S45" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AJ45" s="5"/>
       <c r="AK45" s="5"/>
-    </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL45" s="5"/>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>10042</v>
       </c>
@@ -3687,22 +3957,25 @@
       <c r="Q46" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="R46" s="4" t="s">
+      <c r="R46" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="S46" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AJ46" s="5"/>
       <c r="AK46" s="5"/>
-    </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="AJ47" s="5"/>
+      <c r="AL46" s="5"/>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.2">
       <c r="AK47" s="5"/>
-    </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="AJ48" s="5"/>
+      <c r="AL47" s="5"/>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.2">
       <c r="AK48" s="5"/>
+      <c r="AL48" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R4">
+  <autoFilter ref="A4:S4">
     <sortState ref="A5:R46">
       <sortCondition ref="A4"/>
     </sortState>

--- a/Design/config/WorldConfig.xlsx
+++ b/Design/config/WorldConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$S$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$P$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="213">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -354,18 +354,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>商业(0-999)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>农业(0-999)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>金钱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -378,26 +366,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>治安</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>防御</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ArchGold</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArchFood</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArchPeople</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Gold</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -410,10 +382,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Secure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Wall</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -774,6 +742,14 @@
   </si>
   <si>
     <t>-30,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1172,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL48"/>
+  <dimension ref="A1:AG48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1180,13 +1156,13 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="9.625" customWidth="1"/>
-    <col min="8" max="16" width="9" customWidth="1"/>
-    <col min="17" max="17" width="49.375" customWidth="1"/>
-    <col min="18" max="18" width="12.75" customWidth="1"/>
-    <col min="19" max="19" width="12.125" customWidth="1"/>
+    <col min="8" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="49.375" customWidth="1"/>
+    <col min="15" max="15" width="12.75" customWidth="1"/>
+    <col min="16" max="16" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1197,10 +1173,10 @@
         <v>96</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>14</v>
@@ -1212,40 +1188,31 @@
         <v>101</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>109</v>
+        <v>174</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1271,40 +1238,31 @@
         <v>102</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>111</v>
+        <v>211</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1345,25 +1303,16 @@
         <v>10</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="S3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1404,25 +1353,16 @@
         <v>5</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10001</v>
       </c>
@@ -1430,7 +1370,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D5" s="4">
         <v>789</v>
@@ -1448,38 +1388,29 @@
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="K5" s="4">
-        <v>16600</v>
+        <v>100</v>
       </c>
       <c r="L5" s="4">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="M5" s="4">
-        <v>1700</v>
-      </c>
-      <c r="N5" s="4">
-        <v>4000</v>
-      </c>
-      <c r="O5" s="4">
-        <v>70</v>
-      </c>
-      <c r="P5" s="4">
-        <v>180</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="R5" s="6"/>
-      <c r="S5" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="O5" s="6"/>
+      <c r="P5" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10002</v>
       </c>
@@ -1505,40 +1436,31 @@
         <v>2</v>
       </c>
       <c r="I6" s="4">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4">
-        <v>275</v>
+        <v>100</v>
       </c>
       <c r="K6" s="4">
-        <v>25000</v>
+        <v>100</v>
       </c>
       <c r="L6" s="4">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="M6" s="4">
-        <v>2500</v>
-      </c>
-      <c r="N6" s="4">
-        <v>4500</v>
-      </c>
-      <c r="O6" s="4">
-        <v>80</v>
-      </c>
-      <c r="P6" s="4">
-        <v>210</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10003</v>
       </c>
@@ -1564,42 +1486,33 @@
         <v>2</v>
       </c>
       <c r="I7" s="4">
-        <v>275</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K7" s="4">
-        <v>21600</v>
+        <v>100</v>
       </c>
       <c r="L7" s="4">
-        <v>2600</v>
+        <v>100</v>
       </c>
       <c r="M7" s="4">
-        <v>2300</v>
-      </c>
-      <c r="N7" s="4">
-        <v>4000</v>
-      </c>
-      <c r="O7" s="4">
-        <v>75</v>
-      </c>
-      <c r="P7" s="4">
-        <v>195</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK7" s="5"/>
-      <c r="AL7" s="5"/>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10004</v>
       </c>
@@ -1625,42 +1538,33 @@
         <v>2</v>
       </c>
       <c r="I8" s="4">
-        <v>375</v>
+        <v>5</v>
       </c>
       <c r="J8" s="4">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="K8" s="4">
-        <v>28300</v>
+        <v>100</v>
       </c>
       <c r="L8" s="4">
-        <v>3500</v>
+        <v>100</v>
       </c>
       <c r="M8" s="4">
-        <v>3200</v>
-      </c>
-      <c r="N8" s="4">
-        <v>5500</v>
-      </c>
-      <c r="O8" s="4">
-        <v>90</v>
-      </c>
-      <c r="P8" s="4">
-        <v>240</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK8" s="5"/>
-      <c r="AL8" s="5"/>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10005</v>
       </c>
@@ -1686,42 +1590,33 @@
         <v>2</v>
       </c>
       <c r="I9" s="4">
-        <v>290</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4">
-        <v>275</v>
+        <v>100</v>
       </c>
       <c r="K9" s="4">
-        <v>23300</v>
+        <v>100</v>
       </c>
       <c r="L9" s="4">
-        <v>2700</v>
+        <v>100</v>
       </c>
       <c r="M9" s="4">
-        <v>2400</v>
-      </c>
-      <c r="N9" s="4">
-        <v>4250</v>
-      </c>
-      <c r="O9" s="4">
-        <v>80</v>
-      </c>
-      <c r="P9" s="4">
-        <v>225</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK9" s="5"/>
-      <c r="AL9" s="5"/>
-    </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10006</v>
       </c>
@@ -1747,40 +1642,31 @@
         <v>2</v>
       </c>
       <c r="I10" s="4">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="K10" s="4">
-        <v>20000</v>
+        <v>100</v>
       </c>
       <c r="L10" s="4">
-        <v>2300</v>
+        <v>100</v>
       </c>
       <c r="M10" s="4">
-        <v>2200</v>
-      </c>
-      <c r="N10" s="4">
-        <v>3500</v>
-      </c>
-      <c r="O10" s="4">
-        <v>70</v>
-      </c>
-      <c r="P10" s="4">
-        <v>195</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="R10" s="6"/>
-      <c r="S10" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK10" s="5"/>
-      <c r="AL10" s="5"/>
-    </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="O10" s="6"/>
+      <c r="P10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10007</v>
       </c>
@@ -1806,42 +1692,33 @@
         <v>2</v>
       </c>
       <c r="I11" s="4">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="K11" s="4">
-        <v>18300</v>
+        <v>100</v>
       </c>
       <c r="L11" s="4">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="M11" s="4">
-        <v>2000</v>
-      </c>
-      <c r="N11" s="4">
-        <v>3250</v>
-      </c>
-      <c r="O11" s="4">
-        <v>70</v>
-      </c>
-      <c r="P11" s="4">
-        <v>180</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK11" s="5"/>
-      <c r="AL11" s="5"/>
-    </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="5"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>10008</v>
       </c>
@@ -1867,42 +1744,33 @@
         <v>2</v>
       </c>
       <c r="I12" s="4">
-        <v>275</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="K12" s="4">
-        <v>21600</v>
+        <v>100</v>
       </c>
       <c r="L12" s="4">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="M12" s="4">
-        <v>2300</v>
-      </c>
-      <c r="N12" s="4">
-        <v>4000</v>
-      </c>
-      <c r="O12" s="4">
-        <v>75</v>
-      </c>
-      <c r="P12" s="4">
-        <v>210</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK12" s="5"/>
-      <c r="AL12" s="5"/>
-    </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>10009</v>
       </c>
@@ -1928,40 +1796,31 @@
         <v>3</v>
       </c>
       <c r="I13" s="4">
-        <v>190</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K13" s="4">
-        <v>14300</v>
+        <v>100</v>
       </c>
       <c r="L13" s="4">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="M13" s="4">
-        <v>1800</v>
-      </c>
-      <c r="N13" s="4">
-        <v>2100</v>
-      </c>
-      <c r="O13" s="4">
-        <v>65</v>
-      </c>
-      <c r="P13" s="4">
-        <v>165</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="R13" s="6"/>
-      <c r="S13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="N13" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="AK13" s="5"/>
-      <c r="AL13" s="5"/>
-    </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="O13" s="6"/>
+      <c r="P13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="5"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10010</v>
       </c>
@@ -1987,42 +1846,33 @@
         <v>3</v>
       </c>
       <c r="I14" s="4">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4">
-        <v>275</v>
+        <v>100</v>
       </c>
       <c r="K14" s="4">
-        <v>20600</v>
+        <v>100</v>
       </c>
       <c r="L14" s="4">
-        <v>2200</v>
+        <v>100</v>
       </c>
       <c r="M14" s="4">
-        <v>2500</v>
-      </c>
-      <c r="N14" s="4">
-        <v>3500</v>
-      </c>
-      <c r="O14" s="4">
-        <v>75</v>
-      </c>
-      <c r="P14" s="4">
-        <v>210</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK14" s="5"/>
-      <c r="AL14" s="5"/>
-    </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>10011</v>
       </c>
@@ -2048,40 +1898,31 @@
         <v>3</v>
       </c>
       <c r="I15" s="4">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K15" s="4">
-        <v>20000</v>
+        <v>100</v>
       </c>
       <c r="L15" s="4">
-        <v>2400</v>
+        <v>100</v>
       </c>
       <c r="M15" s="4">
-        <v>2200</v>
-      </c>
-      <c r="N15" s="4">
-        <v>3250</v>
-      </c>
-      <c r="O15" s="4">
-        <v>70</v>
-      </c>
-      <c r="P15" s="4">
-        <v>180</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="R15" s="6"/>
-      <c r="S15" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="AK15" s="5"/>
-      <c r="AL15" s="5"/>
-    </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="O15" s="6"/>
+      <c r="P15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10012</v>
       </c>
@@ -2107,42 +1948,33 @@
         <v>3</v>
       </c>
       <c r="I16" s="4">
-        <v>340</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="K16" s="4">
-        <v>27300</v>
+        <v>100</v>
       </c>
       <c r="L16" s="4">
-        <v>3200</v>
+        <v>100</v>
       </c>
       <c r="M16" s="4">
-        <v>2900</v>
-      </c>
-      <c r="N16" s="4">
-        <v>4750</v>
-      </c>
-      <c r="O16" s="4">
-        <v>85</v>
-      </c>
-      <c r="P16" s="4">
-        <v>240</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="R16" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="S16" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK16" s="5"/>
-      <c r="AL16" s="5"/>
-    </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF16" s="5"/>
+      <c r="AG16" s="5"/>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>10013</v>
       </c>
@@ -2168,42 +2000,33 @@
         <v>3</v>
       </c>
       <c r="I17" s="4">
-        <v>360</v>
+        <v>6</v>
       </c>
       <c r="J17" s="4">
-        <v>340</v>
+        <v>100</v>
       </c>
       <c r="K17" s="4">
-        <v>29300</v>
+        <v>100</v>
       </c>
       <c r="L17" s="4">
-        <v>3400</v>
+        <v>100</v>
       </c>
       <c r="M17" s="4">
-        <v>3100</v>
-      </c>
-      <c r="N17" s="4">
-        <v>5250</v>
-      </c>
-      <c r="O17" s="4">
-        <v>90</v>
-      </c>
-      <c r="P17" s="4">
-        <v>255</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="AK17" s="5"/>
-      <c r="AL17" s="5"/>
-    </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF17" s="5"/>
+      <c r="AG17" s="5"/>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>10014</v>
       </c>
@@ -2229,42 +2052,33 @@
         <v>3</v>
       </c>
       <c r="I18" s="4">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4">
-        <v>275</v>
+        <v>100</v>
       </c>
       <c r="K18" s="4">
-        <v>23300</v>
+        <v>100</v>
       </c>
       <c r="L18" s="4">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="M18" s="4">
-        <v>2500</v>
-      </c>
-      <c r="N18" s="4">
-        <v>4500</v>
-      </c>
-      <c r="O18" s="4">
-        <v>85</v>
-      </c>
-      <c r="P18" s="4">
-        <v>270</v>
-      </c>
-      <c r="Q18" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="AK18" s="5"/>
-      <c r="AL18" s="5"/>
-    </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF18" s="5"/>
+      <c r="AG18" s="5"/>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>10015</v>
       </c>
@@ -2290,42 +2104,33 @@
         <v>3</v>
       </c>
       <c r="I19" s="4">
-        <v>290</v>
+        <v>3</v>
       </c>
       <c r="J19" s="4">
-        <v>310</v>
+        <v>100</v>
       </c>
       <c r="K19" s="4">
-        <v>25000</v>
+        <v>100</v>
       </c>
       <c r="L19" s="4">
-        <v>2700</v>
+        <v>100</v>
       </c>
       <c r="M19" s="4">
-        <v>2800</v>
-      </c>
-      <c r="N19" s="4">
-        <v>4250</v>
-      </c>
-      <c r="O19" s="4">
-        <v>80</v>
-      </c>
-      <c r="P19" s="4">
-        <v>225</v>
-      </c>
-      <c r="Q19" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="R19" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="AK19" s="5"/>
-      <c r="AL19" s="5"/>
-    </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>10016</v>
       </c>
@@ -2351,40 +2156,31 @@
         <v>4</v>
       </c>
       <c r="I20" s="4">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="K20" s="4">
-        <v>19300</v>
+        <v>100</v>
       </c>
       <c r="L20" s="4">
-        <v>2200</v>
+        <v>100</v>
       </c>
       <c r="M20" s="4">
-        <v>2300</v>
-      </c>
-      <c r="N20" s="4">
-        <v>3500</v>
-      </c>
-      <c r="O20" s="4">
-        <v>70</v>
-      </c>
-      <c r="P20" s="4">
-        <v>195</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="R20" s="6"/>
-      <c r="S20" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AK20" s="5"/>
-      <c r="AL20" s="5"/>
-    </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="O20" s="6"/>
+      <c r="P20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF20" s="5"/>
+      <c r="AG20" s="5"/>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>10017</v>
       </c>
@@ -2410,42 +2206,33 @@
         <v>4</v>
       </c>
       <c r="I21" s="4">
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="J21" s="4">
-        <v>290</v>
+        <v>100</v>
       </c>
       <c r="K21" s="4">
-        <v>24000</v>
+        <v>100</v>
       </c>
       <c r="L21" s="4">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="M21" s="4">
-        <v>2600</v>
-      </c>
-      <c r="N21" s="4">
-        <v>4500</v>
-      </c>
-      <c r="O21" s="4">
-        <v>80</v>
-      </c>
-      <c r="P21" s="4">
-        <v>225</v>
-      </c>
-      <c r="Q21" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="R21" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK21" s="5"/>
-      <c r="AL21" s="5"/>
-    </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="5"/>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>10018</v>
       </c>
@@ -2471,42 +2258,33 @@
         <v>4</v>
       </c>
       <c r="I22" s="4">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K22" s="4">
-        <v>16600</v>
+        <v>100</v>
       </c>
       <c r="L22" s="4">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="M22" s="4">
-        <v>1800</v>
-      </c>
-      <c r="N22" s="4">
-        <v>3750</v>
-      </c>
-      <c r="O22" s="4">
-        <v>75</v>
-      </c>
-      <c r="P22" s="4">
-        <v>240</v>
-      </c>
-      <c r="Q22" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="R22" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AK22" s="5"/>
-      <c r="AL22" s="5"/>
-    </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF22" s="5"/>
+      <c r="AG22" s="5"/>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>10019</v>
       </c>
@@ -2532,42 +2310,33 @@
         <v>4</v>
       </c>
       <c r="I23" s="4">
-        <v>350</v>
+        <v>4</v>
       </c>
       <c r="J23" s="4">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="K23" s="4">
-        <v>28300</v>
+        <v>100</v>
       </c>
       <c r="L23" s="4">
-        <v>3300</v>
+        <v>100</v>
       </c>
       <c r="M23" s="4">
-        <v>2900</v>
-      </c>
-      <c r="N23" s="4">
-        <v>5500</v>
-      </c>
-      <c r="O23" s="4">
-        <v>85</v>
-      </c>
-      <c r="P23" s="4">
-        <v>270</v>
-      </c>
-      <c r="Q23" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="R23" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AK23" s="5"/>
-      <c r="AL23" s="5"/>
-    </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF23" s="5"/>
+      <c r="AG23" s="5"/>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>10020</v>
       </c>
@@ -2593,42 +2362,33 @@
         <v>5</v>
       </c>
       <c r="I24" s="4">
-        <v>400</v>
+        <v>7</v>
       </c>
       <c r="J24" s="4">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="K24" s="4">
-        <v>31600</v>
+        <v>100</v>
       </c>
       <c r="L24" s="4">
-        <v>4000</v>
+        <v>100</v>
       </c>
       <c r="M24" s="4">
-        <v>3500</v>
-      </c>
-      <c r="N24" s="4">
-        <v>6000</v>
-      </c>
-      <c r="O24" s="4">
-        <v>95</v>
-      </c>
-      <c r="P24" s="4">
-        <v>285</v>
-      </c>
-      <c r="Q24" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK24" s="5"/>
-      <c r="AL24" s="5"/>
-    </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF24" s="5"/>
+      <c r="AG24" s="5"/>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>10021</v>
       </c>
@@ -2654,42 +2414,33 @@
         <v>5</v>
       </c>
       <c r="I25" s="4">
-        <v>390</v>
+        <v>6</v>
       </c>
       <c r="J25" s="4">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="K25" s="4">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="L25" s="4">
-        <v>3800</v>
+        <v>100</v>
       </c>
       <c r="M25" s="4">
-        <v>3200</v>
-      </c>
-      <c r="N25" s="4">
-        <v>5750</v>
-      </c>
-      <c r="O25" s="4">
-        <v>90</v>
-      </c>
-      <c r="P25" s="4">
-        <v>270</v>
-      </c>
-      <c r="Q25" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="R25" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK25" s="5"/>
-      <c r="AL25" s="5"/>
-    </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF25" s="5"/>
+      <c r="AG25" s="5"/>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>10022</v>
       </c>
@@ -2715,42 +2466,33 @@
         <v>5</v>
       </c>
       <c r="I26" s="4">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="J26" s="4">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="K26" s="4">
-        <v>16000</v>
+        <v>100</v>
       </c>
       <c r="L26" s="4">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="M26" s="4">
-        <v>1900</v>
-      </c>
-      <c r="N26" s="4">
-        <v>3500</v>
-      </c>
-      <c r="O26" s="4">
-        <v>75</v>
-      </c>
-      <c r="P26" s="4">
-        <v>240</v>
-      </c>
-      <c r="Q26" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="R26" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="S26" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK26" s="5"/>
-      <c r="AL26" s="5"/>
-    </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF26" s="5"/>
+      <c r="AG26" s="5"/>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>10023</v>
       </c>
@@ -2776,42 +2518,33 @@
         <v>6</v>
       </c>
       <c r="I27" s="4">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="J27" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K27" s="4">
-        <v>16600</v>
+        <v>100</v>
       </c>
       <c r="L27" s="4">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="M27" s="4">
-        <v>1800</v>
-      </c>
-      <c r="N27" s="4">
-        <v>3750</v>
-      </c>
-      <c r="O27" s="4">
-        <v>75</v>
-      </c>
-      <c r="P27" s="4">
-        <v>255</v>
-      </c>
-      <c r="Q27" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="R27" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="S27" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK27" s="5"/>
-      <c r="AL27" s="5"/>
-    </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF27" s="5"/>
+      <c r="AG27" s="5"/>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>10024</v>
       </c>
@@ -2837,42 +2570,33 @@
         <v>6</v>
       </c>
       <c r="I28" s="4">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="K28" s="4">
-        <v>11600</v>
+        <v>100</v>
       </c>
       <c r="L28" s="4">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="M28" s="4">
-        <v>1400</v>
-      </c>
-      <c r="N28" s="4">
-        <v>3250</v>
-      </c>
-      <c r="O28" s="4">
-        <v>70</v>
-      </c>
-      <c r="P28" s="4">
-        <v>240</v>
-      </c>
-      <c r="Q28" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="R28" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="S28" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK28" s="5"/>
-      <c r="AL28" s="5"/>
-    </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF28" s="5"/>
+      <c r="AG28" s="5"/>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>10025</v>
       </c>
@@ -2898,42 +2622,33 @@
         <v>7</v>
       </c>
       <c r="I29" s="4">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="J29" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K29" s="4">
-        <v>15000</v>
+        <v>100</v>
       </c>
       <c r="L29" s="4">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="M29" s="4">
-        <v>1800</v>
-      </c>
-      <c r="N29" s="4">
-        <v>2250</v>
-      </c>
-      <c r="O29" s="4">
-        <v>70</v>
-      </c>
-      <c r="P29" s="4">
-        <v>180</v>
-      </c>
-      <c r="Q29" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="R29" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="S29" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK29" s="5"/>
-      <c r="AL29" s="5"/>
-    </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="O29" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF29" s="5"/>
+      <c r="AG29" s="5"/>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>10026</v>
       </c>
@@ -2959,42 +2674,33 @@
         <v>7</v>
       </c>
       <c r="I30" s="4">
-        <v>190</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="K30" s="4">
-        <v>14000</v>
+        <v>100</v>
       </c>
       <c r="L30" s="4">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="M30" s="4">
-        <v>1900</v>
-      </c>
-      <c r="N30" s="4">
-        <v>2000</v>
-      </c>
-      <c r="O30" s="4">
-        <v>65</v>
-      </c>
-      <c r="P30" s="4">
-        <v>165</v>
-      </c>
-      <c r="Q30" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="R30" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="S30" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK30" s="5"/>
-      <c r="AL30" s="5"/>
-    </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF30" s="5"/>
+      <c r="AG30" s="5"/>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>10027</v>
       </c>
@@ -3020,42 +2726,33 @@
         <v>7</v>
       </c>
       <c r="I31" s="4">
-        <v>275</v>
+        <v>3</v>
       </c>
       <c r="J31" s="4">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="K31" s="4">
-        <v>23300</v>
+        <v>100</v>
       </c>
       <c r="L31" s="4">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="M31" s="4">
-        <v>2200</v>
-      </c>
-      <c r="N31" s="4">
-        <v>4000</v>
-      </c>
-      <c r="O31" s="4">
-        <v>75</v>
-      </c>
-      <c r="P31" s="4">
-        <v>210</v>
-      </c>
-      <c r="Q31" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="R31" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="S31" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK31" s="5"/>
-      <c r="AL31" s="5"/>
-    </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF31" s="5"/>
+      <c r="AG31" s="5"/>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>10028</v>
       </c>
@@ -3081,42 +2778,33 @@
         <v>7</v>
       </c>
       <c r="I32" s="4">
-        <v>325</v>
+        <v>5</v>
       </c>
       <c r="J32" s="4">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K32" s="4">
-        <v>26600</v>
+        <v>100</v>
       </c>
       <c r="L32" s="4">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="M32" s="4">
-        <v>2800</v>
-      </c>
-      <c r="N32" s="4">
-        <v>6000</v>
-      </c>
-      <c r="O32" s="4">
-        <v>85</v>
-      </c>
-      <c r="P32" s="4">
-        <v>270</v>
-      </c>
-      <c r="Q32" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="R32" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="S32" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK32" s="5"/>
-      <c r="AL32" s="5"/>
-    </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF32" s="5"/>
+      <c r="AG32" s="5"/>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>10029</v>
       </c>
@@ -3142,42 +2830,33 @@
         <v>7</v>
       </c>
       <c r="I33" s="4">
-        <v>275</v>
+        <v>3</v>
       </c>
       <c r="J33" s="4">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="K33" s="4">
-        <v>21600</v>
+        <v>100</v>
       </c>
       <c r="L33" s="4">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="M33" s="4">
-        <v>2300</v>
-      </c>
-      <c r="N33" s="4">
-        <v>4000</v>
-      </c>
-      <c r="O33" s="4">
-        <v>80</v>
-      </c>
-      <c r="P33" s="4">
-        <v>255</v>
-      </c>
-      <c r="Q33" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="R33" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="S33" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK33" s="5"/>
-      <c r="AL33" s="5"/>
-    </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF33" s="5"/>
+      <c r="AG33" s="5"/>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>10030</v>
       </c>
@@ -3203,42 +2882,33 @@
         <v>8</v>
       </c>
       <c r="I34" s="4">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="J34" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K34" s="4">
-        <v>13300</v>
+        <v>100</v>
       </c>
       <c r="L34" s="4">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="M34" s="4">
-        <v>1200</v>
-      </c>
-      <c r="N34" s="4">
-        <v>3000</v>
-      </c>
-      <c r="O34" s="4">
-        <v>75</v>
-      </c>
-      <c r="P34" s="4">
-        <v>240</v>
-      </c>
-      <c r="Q34" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="R34" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="S34" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK34" s="5"/>
-      <c r="AL34" s="5"/>
-    </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF34" s="5"/>
+      <c r="AG34" s="5"/>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>10031</v>
       </c>
@@ -3264,42 +2934,33 @@
         <v>8</v>
       </c>
       <c r="I35" s="4">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="J35" s="4">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="K35" s="4">
-        <v>16600</v>
+        <v>100</v>
       </c>
       <c r="L35" s="4">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="M35" s="4">
-        <v>2000</v>
-      </c>
-      <c r="N35" s="4">
-        <v>2750</v>
-      </c>
-      <c r="O35" s="4">
-        <v>70</v>
-      </c>
-      <c r="P35" s="4">
-        <v>195</v>
-      </c>
-      <c r="Q35" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="R35" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="S35" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK35" s="5"/>
-      <c r="AL35" s="5"/>
-    </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF35" s="5"/>
+      <c r="AG35" s="5"/>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>10032</v>
       </c>
@@ -3325,42 +2986,33 @@
         <v>8</v>
       </c>
       <c r="I36" s="4">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="J36" s="4">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="K36" s="4">
-        <v>11600</v>
+        <v>100</v>
       </c>
       <c r="L36" s="4">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="M36" s="4">
-        <v>1500</v>
-      </c>
-      <c r="N36" s="4">
-        <v>1750</v>
-      </c>
-      <c r="O36" s="4">
-        <v>60</v>
-      </c>
-      <c r="P36" s="4">
-        <v>150</v>
-      </c>
-      <c r="Q36" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="R36" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="S36" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK36" s="5"/>
-      <c r="AL36" s="5"/>
-    </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF36" s="5"/>
+      <c r="AG36" s="5"/>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>10033</v>
       </c>
@@ -3386,42 +3038,33 @@
         <v>8</v>
       </c>
       <c r="I37" s="4">
-        <v>350</v>
+        <v>5</v>
       </c>
       <c r="J37" s="4">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="K37" s="4">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="L37" s="4">
-        <v>3500</v>
+        <v>100</v>
       </c>
       <c r="M37" s="4">
-        <v>4000</v>
-      </c>
-      <c r="N37" s="4">
-        <v>5000</v>
-      </c>
-      <c r="O37" s="4">
-        <v>85</v>
-      </c>
-      <c r="P37" s="4">
-        <v>225</v>
-      </c>
-      <c r="Q37" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="R37" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="S37" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK37" s="5"/>
-      <c r="AL37" s="5"/>
-    </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF37" s="5"/>
+      <c r="AG37" s="5"/>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>10034</v>
       </c>
@@ -3447,42 +3090,33 @@
         <v>8</v>
       </c>
       <c r="I38" s="4">
+        <v>1</v>
+      </c>
+      <c r="J38" s="4">
+        <v>100</v>
+      </c>
+      <c r="K38" s="4">
+        <v>100</v>
+      </c>
+      <c r="L38" s="4">
+        <v>100</v>
+      </c>
+      <c r="M38" s="4">
+        <v>100</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="P38" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="J38" s="4">
-        <v>150</v>
-      </c>
-      <c r="K38" s="4">
-        <v>10000</v>
-      </c>
-      <c r="L38" s="4">
-        <v>1000</v>
-      </c>
-      <c r="M38" s="4">
-        <v>1300</v>
-      </c>
-      <c r="N38" s="4">
-        <v>1500</v>
-      </c>
-      <c r="O38" s="4">
-        <v>55</v>
-      </c>
-      <c r="P38" s="4">
-        <v>135</v>
-      </c>
-      <c r="Q38" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="R38" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="S38" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK38" s="5"/>
-      <c r="AL38" s="5"/>
-    </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AF38" s="5"/>
+      <c r="AG38" s="5"/>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>10035</v>
       </c>
@@ -3490,7 +3124,7 @@
         <v>58</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D39" s="4">
         <v>43</v>
@@ -3508,40 +3142,31 @@
         <v>8</v>
       </c>
       <c r="I39" s="4">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="J39" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K39" s="4">
-        <v>16000</v>
+        <v>100</v>
       </c>
       <c r="L39" s="4">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="M39" s="4">
-        <v>1800</v>
-      </c>
-      <c r="N39" s="4">
-        <v>3250</v>
-      </c>
-      <c r="O39" s="4">
-        <v>75</v>
-      </c>
-      <c r="P39" s="4">
-        <v>225</v>
-      </c>
-      <c r="Q39" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="R39" s="6"/>
-      <c r="S39" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK39" s="5"/>
-      <c r="AL39" s="5"/>
-    </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="O39" s="6"/>
+      <c r="P39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF39" s="5"/>
+      <c r="AG39" s="5"/>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>10036</v>
       </c>
@@ -3567,42 +3192,33 @@
         <v>9</v>
       </c>
       <c r="I40" s="4">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="J40" s="4">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="K40" s="4">
-        <v>15000</v>
+        <v>100</v>
       </c>
       <c r="L40" s="4">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="M40" s="4">
-        <v>1600</v>
-      </c>
-      <c r="N40" s="4">
-        <v>2500</v>
-      </c>
-      <c r="O40" s="4">
-        <v>65</v>
-      </c>
-      <c r="P40" s="4">
-        <v>180</v>
-      </c>
-      <c r="Q40" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="R40" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="S40" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK40" s="5"/>
-      <c r="AL40" s="5"/>
-    </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF40" s="5"/>
+      <c r="AG40" s="5"/>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>10037</v>
       </c>
@@ -3628,42 +3244,33 @@
         <v>9</v>
       </c>
       <c r="I41" s="4">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="J41" s="4">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="K41" s="4">
-        <v>20000</v>
+        <v>100</v>
       </c>
       <c r="L41" s="4">
-        <v>2200</v>
+        <v>100</v>
       </c>
       <c r="M41" s="4">
-        <v>2000</v>
-      </c>
-      <c r="N41" s="4">
-        <v>4250</v>
-      </c>
-      <c r="O41" s="4">
-        <v>80</v>
-      </c>
-      <c r="P41" s="4">
-        <v>255</v>
-      </c>
-      <c r="Q41" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="R41" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="S41" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK41" s="5"/>
-      <c r="AL41" s="5"/>
-    </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF41" s="5"/>
+      <c r="AG41" s="5"/>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>10038</v>
       </c>
@@ -3689,42 +3296,33 @@
         <v>10</v>
       </c>
       <c r="I42" s="4">
-        <v>260</v>
+        <v>4</v>
       </c>
       <c r="J42" s="4">
-        <v>290</v>
+        <v>100</v>
       </c>
       <c r="K42" s="4">
-        <v>22600</v>
+        <v>100</v>
       </c>
       <c r="L42" s="4">
-        <v>2400</v>
+        <v>100</v>
       </c>
       <c r="M42" s="4">
-        <v>2600</v>
-      </c>
-      <c r="N42" s="4">
-        <v>3750</v>
-      </c>
-      <c r="O42" s="4">
-        <v>75</v>
-      </c>
-      <c r="P42" s="4">
-        <v>195</v>
-      </c>
-      <c r="Q42" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="R42" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="S42" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AK42" s="5"/>
-      <c r="AL42" s="5"/>
-    </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF42" s="5"/>
+      <c r="AG42" s="5"/>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>10039</v>
       </c>
@@ -3750,42 +3348,33 @@
         <v>10</v>
       </c>
       <c r="I43" s="4">
-        <v>290</v>
+        <v>4</v>
       </c>
       <c r="J43" s="4">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K43" s="4">
-        <v>24000</v>
+        <v>100</v>
       </c>
       <c r="L43" s="4">
-        <v>2600</v>
+        <v>100</v>
       </c>
       <c r="M43" s="4">
-        <v>2700</v>
-      </c>
-      <c r="N43" s="4">
-        <v>4250</v>
-      </c>
-      <c r="O43" s="4">
-        <v>80</v>
-      </c>
-      <c r="P43" s="4">
-        <v>225</v>
-      </c>
-      <c r="Q43" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="R43" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="S43" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK43" s="5"/>
-      <c r="AL43" s="5"/>
-    </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF43" s="5"/>
+      <c r="AG43" s="5"/>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>10040</v>
       </c>
@@ -3811,40 +3400,31 @@
         <v>11</v>
       </c>
       <c r="I44" s="4">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="J44" s="4">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="K44" s="4">
-        <v>17300</v>
+        <v>100</v>
       </c>
       <c r="L44" s="4">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="M44" s="4">
-        <v>2000</v>
-      </c>
-      <c r="N44" s="4">
-        <v>4000</v>
-      </c>
-      <c r="O44" s="4">
-        <v>80</v>
-      </c>
-      <c r="P44" s="4">
-        <v>255</v>
-      </c>
-      <c r="Q44" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="R44" s="6"/>
-      <c r="S44" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AK44" s="5"/>
-      <c r="AL44" s="5"/>
-    </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="O44" s="6"/>
+      <c r="P44" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF44" s="5"/>
+      <c r="AG44" s="5"/>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>10041</v>
       </c>
@@ -3852,7 +3432,7 @@
         <v>87</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D45" s="4">
         <v>980</v>
@@ -3870,42 +3450,33 @@
         <v>11</v>
       </c>
       <c r="I45" s="4">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="J45" s="4">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="K45" s="4">
-        <v>20000</v>
+        <v>100</v>
       </c>
       <c r="L45" s="4">
-        <v>2300</v>
+        <v>100</v>
       </c>
       <c r="M45" s="4">
-        <v>2200</v>
-      </c>
-      <c r="N45" s="4">
-        <v>4250</v>
-      </c>
-      <c r="O45" s="4">
-        <v>80</v>
-      </c>
-      <c r="P45" s="4">
-        <v>255</v>
-      </c>
-      <c r="Q45" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="R45" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="S45" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AK45" s="5"/>
-      <c r="AL45" s="5"/>
-    </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF45" s="5"/>
+      <c r="AG45" s="5"/>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>10042</v>
       </c>
@@ -3913,7 +3484,7 @@
         <v>94</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D46" s="4">
         <v>1558</v>
@@ -3931,51 +3502,42 @@
         <v>12</v>
       </c>
       <c r="I46" s="4">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="J46" s="4">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="K46" s="4">
-        <v>13300</v>
+        <v>100</v>
       </c>
       <c r="L46" s="4">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="M46" s="4">
-        <v>1700</v>
-      </c>
-      <c r="N46" s="4">
-        <v>3000</v>
-      </c>
-      <c r="O46" s="4">
-        <v>70</v>
-      </c>
-      <c r="P46" s="4">
-        <v>225</v>
-      </c>
-      <c r="Q46" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="R46" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="S46" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK46" s="5"/>
-      <c r="AL46" s="5"/>
-    </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="AK47" s="5"/>
-      <c r="AL47" s="5"/>
-    </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="AK48" s="5"/>
-      <c r="AL48" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF46" s="5"/>
+      <c r="AG46" s="5"/>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AF47" s="5"/>
+      <c r="AG47" s="5"/>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AF48" s="5"/>
+      <c r="AG48" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:S4">
+  <autoFilter ref="A4:P4">
     <sortState ref="A5:R46">
       <sortCondition ref="A4"/>
     </sortState>

--- a/Design/config/WorldConfig.xlsx
+++ b/Design/config/WorldConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$N$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="209">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -354,27 +354,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>金钱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>食物</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>士兵</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>防御</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Food</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1148,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG48"/>
+  <dimension ref="A1:AE48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1156,13 +1140,13 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="9.625" customWidth="1"/>
-    <col min="8" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="49.375" customWidth="1"/>
-    <col min="15" max="15" width="12.75" customWidth="1"/>
-    <col min="16" max="16" width="12.125" customWidth="1"/>
+    <col min="8" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="49.375" customWidth="1"/>
+    <col min="13" max="13" width="12.75" customWidth="1"/>
+    <col min="14" max="14" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,10 +1157,10 @@
         <v>96</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>14</v>
@@ -1188,7 +1172,7 @@
         <v>101</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>103</v>
@@ -1197,22 +1181,16 @@
         <v>104</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1238,31 +1216,25 @@
         <v>102</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1297,22 +1269,16 @@
         <v>10</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="P3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1347,22 +1313,16 @@
         <v>5</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10001</v>
       </c>
@@ -1370,7 +1330,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D5" s="4">
         <v>789</v>
@@ -1396,21 +1356,15 @@
       <c r="K5" s="4">
         <v>100</v>
       </c>
-      <c r="L5" s="4">
-        <v>100</v>
-      </c>
-      <c r="M5" s="4">
-        <v>100</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="O5" s="6"/>
-      <c r="P5" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L5" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="M5" s="6"/>
+      <c r="N5" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10002</v>
       </c>
@@ -1444,23 +1398,17 @@
       <c r="K6" s="4">
         <v>100</v>
       </c>
-      <c r="L6" s="4">
-        <v>100</v>
-      </c>
-      <c r="M6" s="4">
-        <v>100</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10003</v>
       </c>
@@ -1494,25 +1442,19 @@
       <c r="K7" s="4">
         <v>100</v>
       </c>
-      <c r="L7" s="4">
-        <v>100</v>
-      </c>
-      <c r="M7" s="4">
-        <v>100</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF7" s="5"/>
-      <c r="AG7" s="5"/>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L7" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10004</v>
       </c>
@@ -1546,25 +1488,19 @@
       <c r="K8" s="4">
         <v>100</v>
       </c>
-      <c r="L8" s="4">
-        <v>100</v>
-      </c>
-      <c r="M8" s="4">
-        <v>100</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="AF8" s="5"/>
-      <c r="AG8" s="5"/>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L8" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10005</v>
       </c>
@@ -1598,25 +1534,19 @@
       <c r="K9" s="4">
         <v>100</v>
       </c>
-      <c r="L9" s="4">
-        <v>100</v>
-      </c>
-      <c r="M9" s="4">
-        <v>100</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF9" s="5"/>
-      <c r="AG9" s="5"/>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L9" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10006</v>
       </c>
@@ -1650,23 +1580,17 @@
       <c r="K10" s="4">
         <v>100</v>
       </c>
-      <c r="L10" s="4">
-        <v>100</v>
-      </c>
-      <c r="M10" s="4">
-        <v>100</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="O10" s="6"/>
-      <c r="P10" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L10" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="M10" s="6"/>
+      <c r="N10" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10007</v>
       </c>
@@ -1700,25 +1624,19 @@
       <c r="K11" s="4">
         <v>100</v>
       </c>
-      <c r="L11" s="4">
-        <v>100</v>
-      </c>
-      <c r="M11" s="4">
-        <v>100</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF11" s="5"/>
-      <c r="AG11" s="5"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L11" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="5"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>10008</v>
       </c>
@@ -1752,25 +1670,19 @@
       <c r="K12" s="4">
         <v>100</v>
       </c>
-      <c r="L12" s="4">
-        <v>100</v>
-      </c>
-      <c r="M12" s="4">
-        <v>100</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF12" s="5"/>
-      <c r="AG12" s="5"/>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L12" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>10009</v>
       </c>
@@ -1804,23 +1716,17 @@
       <c r="K13" s="4">
         <v>100</v>
       </c>
-      <c r="L13" s="4">
-        <v>100</v>
-      </c>
-      <c r="M13" s="4">
-        <v>100</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="O13" s="6"/>
-      <c r="P13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="5"/>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L13" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M13" s="6"/>
+      <c r="N13" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10010</v>
       </c>
@@ -1854,25 +1760,19 @@
       <c r="K14" s="4">
         <v>100</v>
       </c>
-      <c r="L14" s="4">
-        <v>100</v>
-      </c>
-      <c r="M14" s="4">
-        <v>100</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF14" s="5"/>
-      <c r="AG14" s="5"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L14" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>10011</v>
       </c>
@@ -1906,23 +1806,17 @@
       <c r="K15" s="4">
         <v>100</v>
       </c>
-      <c r="L15" s="4">
-        <v>100</v>
-      </c>
-      <c r="M15" s="4">
-        <v>100</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="O15" s="6"/>
-      <c r="P15" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF15" s="5"/>
-      <c r="AG15" s="5"/>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L15" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M15" s="6"/>
+      <c r="N15" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10012</v>
       </c>
@@ -1956,25 +1850,19 @@
       <c r="K16" s="4">
         <v>100</v>
       </c>
-      <c r="L16" s="4">
-        <v>100</v>
-      </c>
-      <c r="M16" s="4">
-        <v>100</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF16" s="5"/>
-      <c r="AG16" s="5"/>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L16" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="5"/>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>10013</v>
       </c>
@@ -2008,25 +1896,19 @@
       <c r="K17" s="4">
         <v>100</v>
       </c>
-      <c r="L17" s="4">
-        <v>100</v>
-      </c>
-      <c r="M17" s="4">
-        <v>100</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF17" s="5"/>
-      <c r="AG17" s="5"/>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L17" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD17" s="5"/>
+      <c r="AE17" s="5"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>10014</v>
       </c>
@@ -2060,25 +1942,19 @@
       <c r="K18" s="4">
         <v>100</v>
       </c>
-      <c r="L18" s="4">
-        <v>100</v>
-      </c>
-      <c r="M18" s="4">
-        <v>100</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF18" s="5"/>
-      <c r="AG18" s="5"/>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L18" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>10015</v>
       </c>
@@ -2112,25 +1988,19 @@
       <c r="K19" s="4">
         <v>100</v>
       </c>
-      <c r="L19" s="4">
-        <v>100</v>
-      </c>
-      <c r="M19" s="4">
-        <v>100</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="AF19" s="5"/>
-      <c r="AG19" s="5"/>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L19" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="5"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>10016</v>
       </c>
@@ -2164,23 +2034,17 @@
       <c r="K20" s="4">
         <v>100</v>
       </c>
-      <c r="L20" s="4">
-        <v>100</v>
-      </c>
-      <c r="M20" s="4">
-        <v>100</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="O20" s="6"/>
-      <c r="P20" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF20" s="5"/>
-      <c r="AG20" s="5"/>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L20" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="M20" s="6"/>
+      <c r="N20" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="5"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>10017</v>
       </c>
@@ -2214,25 +2078,19 @@
       <c r="K21" s="4">
         <v>100</v>
       </c>
-      <c r="L21" s="4">
-        <v>100</v>
-      </c>
-      <c r="M21" s="4">
-        <v>100</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="O21" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF21" s="5"/>
-      <c r="AG21" s="5"/>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L21" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>10018</v>
       </c>
@@ -2266,25 +2124,19 @@
       <c r="K22" s="4">
         <v>100</v>
       </c>
-      <c r="L22" s="4">
-        <v>100</v>
-      </c>
-      <c r="M22" s="4">
-        <v>100</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF22" s="5"/>
-      <c r="AG22" s="5"/>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L22" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="5"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>10019</v>
       </c>
@@ -2318,25 +2170,19 @@
       <c r="K23" s="4">
         <v>100</v>
       </c>
-      <c r="L23" s="4">
-        <v>100</v>
-      </c>
-      <c r="M23" s="4">
-        <v>100</v>
-      </c>
-      <c r="N23" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="O23" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AF23" s="5"/>
-      <c r="AG23" s="5"/>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L23" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD23" s="5"/>
+      <c r="AE23" s="5"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>10020</v>
       </c>
@@ -2370,25 +2216,19 @@
       <c r="K24" s="4">
         <v>100</v>
       </c>
-      <c r="L24" s="4">
-        <v>100</v>
-      </c>
-      <c r="M24" s="4">
-        <v>100</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="AF24" s="5"/>
-      <c r="AG24" s="5"/>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L24" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="5"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>10021</v>
       </c>
@@ -2422,25 +2262,19 @@
       <c r="K25" s="4">
         <v>100</v>
       </c>
-      <c r="L25" s="4">
-        <v>100</v>
-      </c>
-      <c r="M25" s="4">
-        <v>100</v>
-      </c>
-      <c r="N25" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="O25" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="AF25" s="5"/>
-      <c r="AG25" s="5"/>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L25" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD25" s="5"/>
+      <c r="AE25" s="5"/>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>10022</v>
       </c>
@@ -2474,25 +2308,19 @@
       <c r="K26" s="4">
         <v>100</v>
       </c>
-      <c r="L26" s="4">
-        <v>100</v>
-      </c>
-      <c r="M26" s="4">
-        <v>100</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF26" s="5"/>
-      <c r="AG26" s="5"/>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L26" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD26" s="5"/>
+      <c r="AE26" s="5"/>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>10023</v>
       </c>
@@ -2526,25 +2354,19 @@
       <c r="K27" s="4">
         <v>100</v>
       </c>
-      <c r="L27" s="4">
-        <v>100</v>
-      </c>
-      <c r="M27" s="4">
-        <v>100</v>
-      </c>
-      <c r="N27" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="O27" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF27" s="5"/>
-      <c r="AG27" s="5"/>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L27" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="5"/>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>10024</v>
       </c>
@@ -2578,25 +2400,19 @@
       <c r="K28" s="4">
         <v>100</v>
       </c>
-      <c r="L28" s="4">
-        <v>100</v>
-      </c>
-      <c r="M28" s="4">
-        <v>100</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF28" s="5"/>
-      <c r="AG28" s="5"/>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L28" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD28" s="5"/>
+      <c r="AE28" s="5"/>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>10025</v>
       </c>
@@ -2630,25 +2446,19 @@
       <c r="K29" s="4">
         <v>100</v>
       </c>
-      <c r="L29" s="4">
-        <v>100</v>
-      </c>
-      <c r="M29" s="4">
-        <v>100</v>
-      </c>
-      <c r="N29" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="P29" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF29" s="5"/>
-      <c r="AG29" s="5"/>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L29" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD29" s="5"/>
+      <c r="AE29" s="5"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>10026</v>
       </c>
@@ -2682,25 +2492,19 @@
       <c r="K30" s="4">
         <v>100</v>
       </c>
-      <c r="L30" s="4">
-        <v>100</v>
-      </c>
-      <c r="M30" s="4">
-        <v>100</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="P30" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF30" s="5"/>
-      <c r="AG30" s="5"/>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD30" s="5"/>
+      <c r="AE30" s="5"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>10027</v>
       </c>
@@ -2734,25 +2538,19 @@
       <c r="K31" s="4">
         <v>100</v>
       </c>
-      <c r="L31" s="4">
-        <v>100</v>
-      </c>
-      <c r="M31" s="4">
-        <v>100</v>
-      </c>
-      <c r="N31" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="P31" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF31" s="5"/>
-      <c r="AG31" s="5"/>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L31" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD31" s="5"/>
+      <c r="AE31" s="5"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>10028</v>
       </c>
@@ -2786,25 +2584,19 @@
       <c r="K32" s="4">
         <v>100</v>
       </c>
-      <c r="L32" s="4">
-        <v>100</v>
-      </c>
-      <c r="M32" s="4">
-        <v>100</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="P32" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AF32" s="5"/>
-      <c r="AG32" s="5"/>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L32" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD32" s="5"/>
+      <c r="AE32" s="5"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>10029</v>
       </c>
@@ -2838,25 +2630,19 @@
       <c r="K33" s="4">
         <v>100</v>
       </c>
-      <c r="L33" s="4">
-        <v>100</v>
-      </c>
-      <c r="M33" s="4">
-        <v>100</v>
-      </c>
-      <c r="N33" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF33" s="5"/>
-      <c r="AG33" s="5"/>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L33" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD33" s="5"/>
+      <c r="AE33" s="5"/>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>10030</v>
       </c>
@@ -2890,25 +2676,19 @@
       <c r="K34" s="4">
         <v>100</v>
       </c>
-      <c r="L34" s="4">
-        <v>100</v>
-      </c>
-      <c r="M34" s="4">
-        <v>100</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="P34" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF34" s="5"/>
-      <c r="AG34" s="5"/>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L34" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD34" s="5"/>
+      <c r="AE34" s="5"/>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>10031</v>
       </c>
@@ -2942,25 +2722,19 @@
       <c r="K35" s="4">
         <v>100</v>
       </c>
-      <c r="L35" s="4">
-        <v>100</v>
-      </c>
-      <c r="M35" s="4">
-        <v>100</v>
-      </c>
-      <c r="N35" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="O35" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="P35" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF35" s="5"/>
-      <c r="AG35" s="5"/>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L35" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD35" s="5"/>
+      <c r="AE35" s="5"/>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>10032</v>
       </c>
@@ -2994,25 +2768,19 @@
       <c r="K36" s="4">
         <v>100</v>
       </c>
-      <c r="L36" s="4">
-        <v>100</v>
-      </c>
-      <c r="M36" s="4">
-        <v>100</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="P36" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF36" s="5"/>
-      <c r="AG36" s="5"/>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L36" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD36" s="5"/>
+      <c r="AE36" s="5"/>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>10033</v>
       </c>
@@ -3046,25 +2814,19 @@
       <c r="K37" s="4">
         <v>100</v>
       </c>
-      <c r="L37" s="4">
-        <v>100</v>
-      </c>
-      <c r="M37" s="4">
-        <v>100</v>
-      </c>
-      <c r="N37" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="O37" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF37" s="5"/>
-      <c r="AG37" s="5"/>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L37" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD37" s="5"/>
+      <c r="AE37" s="5"/>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>10034</v>
       </c>
@@ -3098,25 +2860,19 @@
       <c r="K38" s="4">
         <v>100</v>
       </c>
-      <c r="L38" s="4">
-        <v>100</v>
-      </c>
-      <c r="M38" s="4">
-        <v>100</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF38" s="5"/>
-      <c r="AG38" s="5"/>
-    </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L38" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD38" s="5"/>
+      <c r="AE38" s="5"/>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>10035</v>
       </c>
@@ -3124,7 +2880,7 @@
         <v>58</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D39" s="4">
         <v>43</v>
@@ -3150,23 +2906,17 @@
       <c r="K39" s="4">
         <v>100</v>
       </c>
-      <c r="L39" s="4">
-        <v>100</v>
-      </c>
-      <c r="M39" s="4">
-        <v>100</v>
-      </c>
-      <c r="N39" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="O39" s="6"/>
-      <c r="P39" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF39" s="5"/>
-      <c r="AG39" s="5"/>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L39" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="M39" s="6"/>
+      <c r="N39" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD39" s="5"/>
+      <c r="AE39" s="5"/>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>10036</v>
       </c>
@@ -3200,25 +2950,19 @@
       <c r="K40" s="4">
         <v>100</v>
       </c>
-      <c r="L40" s="4">
-        <v>100</v>
-      </c>
-      <c r="M40" s="4">
-        <v>100</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF40" s="5"/>
-      <c r="AG40" s="5"/>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L40" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD40" s="5"/>
+      <c r="AE40" s="5"/>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>10037</v>
       </c>
@@ -3252,25 +2996,19 @@
       <c r="K41" s="4">
         <v>100</v>
       </c>
-      <c r="L41" s="4">
-        <v>100</v>
-      </c>
-      <c r="M41" s="4">
-        <v>100</v>
-      </c>
-      <c r="N41" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF41" s="5"/>
-      <c r="AG41" s="5"/>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L41" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD41" s="5"/>
+      <c r="AE41" s="5"/>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>10038</v>
       </c>
@@ -3304,25 +3042,19 @@
       <c r="K42" s="4">
         <v>100</v>
       </c>
-      <c r="L42" s="4">
-        <v>100</v>
-      </c>
-      <c r="M42" s="4">
-        <v>100</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF42" s="5"/>
-      <c r="AG42" s="5"/>
-    </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L42" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD42" s="5"/>
+      <c r="AE42" s="5"/>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>10039</v>
       </c>
@@ -3356,25 +3088,19 @@
       <c r="K43" s="4">
         <v>100</v>
       </c>
-      <c r="L43" s="4">
-        <v>100</v>
-      </c>
-      <c r="M43" s="4">
-        <v>100</v>
-      </c>
-      <c r="N43" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF43" s="5"/>
-      <c r="AG43" s="5"/>
-    </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L43" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD43" s="5"/>
+      <c r="AE43" s="5"/>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>10040</v>
       </c>
@@ -3408,23 +3134,17 @@
       <c r="K44" s="4">
         <v>100</v>
       </c>
-      <c r="L44" s="4">
-        <v>100</v>
-      </c>
-      <c r="M44" s="4">
-        <v>100</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="O44" s="6"/>
-      <c r="P44" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AF44" s="5"/>
-      <c r="AG44" s="5"/>
-    </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L44" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M44" s="6"/>
+      <c r="N44" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD44" s="5"/>
+      <c r="AE44" s="5"/>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>10041</v>
       </c>
@@ -3432,7 +3152,7 @@
         <v>87</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D45" s="4">
         <v>980</v>
@@ -3458,25 +3178,19 @@
       <c r="K45" s="4">
         <v>100</v>
       </c>
-      <c r="L45" s="4">
-        <v>100</v>
-      </c>
-      <c r="M45" s="4">
-        <v>100</v>
-      </c>
-      <c r="N45" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AF45" s="5"/>
-      <c r="AG45" s="5"/>
-    </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="L45" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD45" s="5"/>
+      <c r="AE45" s="5"/>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>10042</v>
       </c>
@@ -3484,7 +3198,7 @@
         <v>94</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D46" s="4">
         <v>1558</v>
@@ -3510,34 +3224,28 @@
       <c r="K46" s="4">
         <v>100</v>
       </c>
-      <c r="L46" s="4">
-        <v>100</v>
-      </c>
-      <c r="M46" s="4">
-        <v>100</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF46" s="5"/>
-      <c r="AG46" s="5"/>
-    </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AF47" s="5"/>
-      <c r="AG47" s="5"/>
-    </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AF48" s="5"/>
-      <c r="AG48" s="5"/>
+      <c r="L46" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD46" s="5"/>
+      <c r="AE46" s="5"/>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD47" s="5"/>
+      <c r="AE47" s="5"/>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD48" s="5"/>
+      <c r="AE48" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P4">
+  <autoFilter ref="A4:N4">
     <sortState ref="A5:R46">
       <sortCondition ref="A4"/>
     </sortState>

--- a/Design/config/WorldConfig.xlsx
+++ b/Design/config/WorldConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="211">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -734,6 +734,14 @@
   </si>
   <si>
     <t>等级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>粮食</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1132,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE48"/>
+  <dimension ref="A1:AF48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1140,13 +1148,13 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="9.625" customWidth="1"/>
-    <col min="8" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="49.375" customWidth="1"/>
-    <col min="13" max="13" width="12.75" customWidth="1"/>
-    <col min="14" max="14" width="12.125" customWidth="1"/>
+    <col min="8" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="49.375" customWidth="1"/>
+    <col min="14" max="14" width="12.75" customWidth="1"/>
+    <col min="15" max="15" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1175,22 +1183,25 @@
         <v>208</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1219,22 +1230,25 @@
         <v>207</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1269,16 +1283,19 @@
         <v>10</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1313,16 +1330,19 @@
         <v>5</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>10001</v>
       </c>
@@ -1356,15 +1376,18 @@
       <c r="K5" s="4">
         <v>100</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="4">
+        <v>100</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="6"/>
+      <c r="O5" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>10002</v>
       </c>
@@ -1398,17 +1421,20 @@
       <c r="K6" s="4">
         <v>100</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="4">
+        <v>100</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>10003</v>
       </c>
@@ -1442,19 +1468,22 @@
       <c r="K7" s="4">
         <v>100</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="4">
+        <v>100</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="N7" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="O7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD7" s="5"/>
       <c r="AE7" s="5"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="5"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>10004</v>
       </c>
@@ -1488,19 +1517,22 @@
       <c r="K8" s="4">
         <v>100</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="4">
+        <v>100</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="N8" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="O8" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="AD8" s="5"/>
       <c r="AE8" s="5"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="5"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>10005</v>
       </c>
@@ -1534,19 +1566,22 @@
       <c r="K9" s="4">
         <v>100</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="4">
+        <v>100</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="N9" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="O9" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD9" s="5"/>
       <c r="AE9" s="5"/>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="5"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>10006</v>
       </c>
@@ -1580,17 +1615,20 @@
       <c r="K10" s="4">
         <v>100</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="4">
+        <v>100</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="6"/>
+      <c r="O10" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD10" s="5"/>
       <c r="AE10" s="5"/>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="5"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10007</v>
       </c>
@@ -1624,19 +1662,22 @@
       <c r="K11" s="4">
         <v>100</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="4">
+        <v>100</v>
+      </c>
+      <c r="M11" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="N11" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="O11" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD11" s="5"/>
       <c r="AE11" s="5"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="5"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>10008</v>
       </c>
@@ -1670,19 +1711,22 @@
       <c r="K12" s="4">
         <v>100</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="4">
+        <v>100</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="N12" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="O12" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD12" s="5"/>
       <c r="AE12" s="5"/>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="5"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>10009</v>
       </c>
@@ -1716,17 +1760,20 @@
       <c r="K13" s="4">
         <v>100</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="4">
+        <v>100</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="6"/>
+      <c r="O13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AD13" s="5"/>
       <c r="AE13" s="5"/>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="5"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10010</v>
       </c>
@@ -1760,19 +1807,22 @@
       <c r="K14" s="4">
         <v>100</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="4">
+        <v>100</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="N14" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="O14" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD14" s="5"/>
       <c r="AE14" s="5"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="5"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>10011</v>
       </c>
@@ -1806,17 +1856,20 @@
       <c r="K15" s="4">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="4">
+        <v>100</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="6"/>
+      <c r="O15" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AD15" s="5"/>
       <c r="AE15" s="5"/>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="5"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10012</v>
       </c>
@@ -1850,19 +1903,22 @@
       <c r="K16" s="4">
         <v>100</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="4">
+        <v>100</v>
+      </c>
+      <c r="M16" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="N16" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="O16" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AD16" s="5"/>
       <c r="AE16" s="5"/>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="5"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>10013</v>
       </c>
@@ -1896,19 +1952,22 @@
       <c r="K17" s="4">
         <v>100</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="4">
+        <v>100</v>
+      </c>
+      <c r="M17" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="N17" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="O17" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AD17" s="5"/>
       <c r="AE17" s="5"/>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="5"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>10014</v>
       </c>
@@ -1942,19 +2001,22 @@
       <c r="K18" s="4">
         <v>100</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="4">
+        <v>100</v>
+      </c>
+      <c r="M18" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="N18" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="N18" s="4" t="s">
+      <c r="O18" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="AD18" s="5"/>
       <c r="AE18" s="5"/>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="5"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>10015</v>
       </c>
@@ -1988,19 +2050,22 @@
       <c r="K19" s="4">
         <v>100</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="4">
+        <v>100</v>
+      </c>
+      <c r="M19" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="M19" s="6" t="s">
+      <c r="N19" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="N19" s="4" t="s">
+      <c r="O19" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="AD19" s="5"/>
       <c r="AE19" s="5"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="5"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>10016</v>
       </c>
@@ -2034,17 +2099,20 @@
       <c r="K20" s="4">
         <v>100</v>
       </c>
-      <c r="L20" s="6" t="s">
+      <c r="L20" s="4">
+        <v>100</v>
+      </c>
+      <c r="M20" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="M20" s="6"/>
-      <c r="N20" s="4" t="s">
+      <c r="N20" s="6"/>
+      <c r="O20" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AD20" s="5"/>
       <c r="AE20" s="5"/>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="5"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>10017</v>
       </c>
@@ -2078,19 +2146,22 @@
       <c r="K21" s="4">
         <v>100</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L21" s="4">
+        <v>100</v>
+      </c>
+      <c r="M21" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="N21" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="O21" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD21" s="5"/>
       <c r="AE21" s="5"/>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="5"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>10018</v>
       </c>
@@ -2124,19 +2195,22 @@
       <c r="K22" s="4">
         <v>100</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="4">
+        <v>100</v>
+      </c>
+      <c r="M22" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="N22" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="O22" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AD22" s="5"/>
       <c r="AE22" s="5"/>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="5"/>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>10019</v>
       </c>
@@ -2170,19 +2244,22 @@
       <c r="K23" s="4">
         <v>100</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="4">
+        <v>100</v>
+      </c>
+      <c r="M23" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="M23" s="6" t="s">
+      <c r="N23" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="N23" s="4" t="s">
+      <c r="O23" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AD23" s="5"/>
       <c r="AE23" s="5"/>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="5"/>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>10020</v>
       </c>
@@ -2216,19 +2293,22 @@
       <c r="K24" s="4">
         <v>100</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="4">
+        <v>100</v>
+      </c>
+      <c r="M24" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="N24" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="O24" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="AD24" s="5"/>
       <c r="AE24" s="5"/>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="5"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>10021</v>
       </c>
@@ -2262,19 +2342,22 @@
       <c r="K25" s="4">
         <v>100</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="4">
+        <v>100</v>
+      </c>
+      <c r="M25" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="M25" s="6" t="s">
+      <c r="N25" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="N25" s="4" t="s">
+      <c r="O25" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="AD25" s="5"/>
       <c r="AE25" s="5"/>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="5"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>10022</v>
       </c>
@@ -2308,19 +2391,22 @@
       <c r="K26" s="4">
         <v>100</v>
       </c>
-      <c r="L26" s="6" t="s">
+      <c r="L26" s="4">
+        <v>100</v>
+      </c>
+      <c r="M26" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="M26" s="6" t="s">
+      <c r="N26" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N26" s="4" t="s">
+      <c r="O26" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="AD26" s="5"/>
       <c r="AE26" s="5"/>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="5"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>10023</v>
       </c>
@@ -2354,19 +2440,22 @@
       <c r="K27" s="4">
         <v>100</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="4">
+        <v>100</v>
+      </c>
+      <c r="M27" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="M27" s="6" t="s">
+      <c r="N27" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="N27" s="4" t="s">
+      <c r="O27" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="AD27" s="5"/>
       <c r="AE27" s="5"/>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="5"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>10024</v>
       </c>
@@ -2400,19 +2489,22 @@
       <c r="K28" s="4">
         <v>100</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="L28" s="4">
+        <v>100</v>
+      </c>
+      <c r="M28" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="M28" s="6" t="s">
+      <c r="N28" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="N28" s="4" t="s">
+      <c r="O28" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="AD28" s="5"/>
       <c r="AE28" s="5"/>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="5"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>10025</v>
       </c>
@@ -2446,19 +2538,22 @@
       <c r="K29" s="4">
         <v>100</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="4">
+        <v>100</v>
+      </c>
+      <c r="M29" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M29" s="6" t="s">
+      <c r="N29" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="N29" s="4" t="s">
+      <c r="O29" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="AD29" s="5"/>
       <c r="AE29" s="5"/>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="5"/>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>10026</v>
       </c>
@@ -2492,19 +2587,22 @@
       <c r="K30" s="4">
         <v>100</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="L30" s="4">
+        <v>100</v>
+      </c>
+      <c r="M30" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="M30" s="6" t="s">
+      <c r="N30" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="N30" s="4" t="s">
+      <c r="O30" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="AD30" s="5"/>
       <c r="AE30" s="5"/>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="5"/>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>10027</v>
       </c>
@@ -2538,19 +2636,22 @@
       <c r="K31" s="4">
         <v>100</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="4">
+        <v>100</v>
+      </c>
+      <c r="M31" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="M31" s="6" t="s">
+      <c r="N31" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="N31" s="4" t="s">
+      <c r="O31" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD31" s="5"/>
       <c r="AE31" s="5"/>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="5"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>10028</v>
       </c>
@@ -2584,19 +2685,22 @@
       <c r="K32" s="4">
         <v>100</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="4">
+        <v>100</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="M32" s="6" t="s">
+      <c r="N32" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="N32" s="4" t="s">
+      <c r="O32" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AD32" s="5"/>
       <c r="AE32" s="5"/>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="5"/>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>10029</v>
       </c>
@@ -2630,19 +2734,22 @@
       <c r="K33" s="4">
         <v>100</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="4">
+        <v>100</v>
+      </c>
+      <c r="M33" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M33" s="6" t="s">
+      <c r="N33" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="N33" s="4" t="s">
+      <c r="O33" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AD33" s="5"/>
       <c r="AE33" s="5"/>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="5"/>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>10030</v>
       </c>
@@ -2676,19 +2783,22 @@
       <c r="K34" s="4">
         <v>100</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="L34" s="4">
+        <v>100</v>
+      </c>
+      <c r="M34" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="M34" s="6" t="s">
+      <c r="N34" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="N34" s="4" t="s">
+      <c r="O34" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="AD34" s="5"/>
       <c r="AE34" s="5"/>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="5"/>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>10031</v>
       </c>
@@ -2722,19 +2832,22 @@
       <c r="K35" s="4">
         <v>100</v>
       </c>
-      <c r="L35" s="6" t="s">
+      <c r="L35" s="4">
+        <v>100</v>
+      </c>
+      <c r="M35" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="M35" s="6" t="s">
+      <c r="N35" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="N35" s="4" t="s">
+      <c r="O35" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AD35" s="5"/>
       <c r="AE35" s="5"/>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="5"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>10032</v>
       </c>
@@ -2768,19 +2881,22 @@
       <c r="K36" s="4">
         <v>100</v>
       </c>
-      <c r="L36" s="6" t="s">
+      <c r="L36" s="4">
+        <v>100</v>
+      </c>
+      <c r="M36" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="M36" s="6" t="s">
+      <c r="N36" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="N36" s="4" t="s">
+      <c r="O36" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AD36" s="5"/>
       <c r="AE36" s="5"/>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF36" s="5"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>10033</v>
       </c>
@@ -2814,19 +2930,22 @@
       <c r="K37" s="4">
         <v>100</v>
       </c>
-      <c r="L37" s="6" t="s">
+      <c r="L37" s="4">
+        <v>100</v>
+      </c>
+      <c r="M37" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="M37" s="6" t="s">
+      <c r="N37" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="N37" s="4" t="s">
+      <c r="O37" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD37" s="5"/>
       <c r="AE37" s="5"/>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF37" s="5"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>10034</v>
       </c>
@@ -2860,19 +2979,22 @@
       <c r="K38" s="4">
         <v>100</v>
       </c>
-      <c r="L38" s="6" t="s">
+      <c r="L38" s="4">
+        <v>100</v>
+      </c>
+      <c r="M38" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="M38" s="6" t="s">
+      <c r="N38" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="N38" s="4" t="s">
+      <c r="O38" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AD38" s="5"/>
       <c r="AE38" s="5"/>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="5"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>10035</v>
       </c>
@@ -2906,17 +3028,20 @@
       <c r="K39" s="4">
         <v>100</v>
       </c>
-      <c r="L39" s="6" t="s">
+      <c r="L39" s="4">
+        <v>100</v>
+      </c>
+      <c r="M39" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="M39" s="6"/>
-      <c r="N39" s="4" t="s">
+      <c r="N39" s="6"/>
+      <c r="O39" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AD39" s="5"/>
       <c r="AE39" s="5"/>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="5"/>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>10036</v>
       </c>
@@ -2950,19 +3075,22 @@
       <c r="K40" s="4">
         <v>100</v>
       </c>
-      <c r="L40" s="6" t="s">
+      <c r="L40" s="4">
+        <v>100</v>
+      </c>
+      <c r="M40" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="M40" s="6" t="s">
+      <c r="N40" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="N40" s="4" t="s">
+      <c r="O40" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AD40" s="5"/>
       <c r="AE40" s="5"/>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="5"/>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>10037</v>
       </c>
@@ -2996,19 +3124,22 @@
       <c r="K41" s="4">
         <v>100</v>
       </c>
-      <c r="L41" s="6" t="s">
+      <c r="L41" s="4">
+        <v>100</v>
+      </c>
+      <c r="M41" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M41" s="6" t="s">
+      <c r="N41" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="N41" s="4" t="s">
+      <c r="O41" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD41" s="5"/>
       <c r="AE41" s="5"/>
-    </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="5"/>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>10038</v>
       </c>
@@ -3042,19 +3173,22 @@
       <c r="K42" s="4">
         <v>100</v>
       </c>
-      <c r="L42" s="6" t="s">
+      <c r="L42" s="4">
+        <v>100</v>
+      </c>
+      <c r="M42" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M42" s="6" t="s">
+      <c r="N42" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="N42" s="4" t="s">
+      <c r="O42" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AD42" s="5"/>
       <c r="AE42" s="5"/>
-    </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="5"/>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>10039</v>
       </c>
@@ -3088,19 +3222,22 @@
       <c r="K43" s="4">
         <v>100</v>
       </c>
-      <c r="L43" s="6" t="s">
+      <c r="L43" s="4">
+        <v>100</v>
+      </c>
+      <c r="M43" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="M43" s="6" t="s">
+      <c r="N43" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="N43" s="4" t="s">
+      <c r="O43" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD43" s="5"/>
       <c r="AE43" s="5"/>
-    </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="5"/>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>10040</v>
       </c>
@@ -3134,17 +3271,20 @@
       <c r="K44" s="4">
         <v>100</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="4">
+        <v>100</v>
+      </c>
+      <c r="M44" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="M44" s="6"/>
-      <c r="N44" s="4" t="s">
+      <c r="N44" s="6"/>
+      <c r="O44" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AD44" s="5"/>
       <c r="AE44" s="5"/>
-    </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="5"/>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>10041</v>
       </c>
@@ -3178,19 +3318,22 @@
       <c r="K45" s="4">
         <v>100</v>
       </c>
-      <c r="L45" s="6" t="s">
+      <c r="L45" s="4">
+        <v>100</v>
+      </c>
+      <c r="M45" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="M45" s="6" t="s">
+      <c r="N45" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="N45" s="4" t="s">
+      <c r="O45" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AD45" s="5"/>
       <c r="AE45" s="5"/>
-    </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="5"/>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>10042</v>
       </c>
@@ -3224,28 +3367,31 @@
       <c r="K46" s="4">
         <v>100</v>
       </c>
-      <c r="L46" s="6" t="s">
+      <c r="L46" s="4">
+        <v>100</v>
+      </c>
+      <c r="M46" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M46" s="6" t="s">
+      <c r="N46" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="N46" s="4" t="s">
+      <c r="O46" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="AD46" s="5"/>
       <c r="AE46" s="5"/>
-    </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="AD47" s="5"/>
+      <c r="AF46" s="5"/>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
       <c r="AE47" s="5"/>
-    </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="AD48" s="5"/>
+      <c r="AF47" s="5"/>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
       <c r="AE48" s="5"/>
+      <c r="AF48" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N4">
+  <autoFilter ref="A4:O4">
     <sortState ref="A5:R46">
       <sortCondition ref="A4"/>
     </sortState>
